--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actions'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actions'!$A$1:$W$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,23 +444,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,52 +495,97 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>due</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>blocked_by</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>origin</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>next_step</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>prerequisites</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>unblocker</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>effort</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>closed</t>
         </is>
       </c>
     </row>
@@ -558,46 +612,63 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -622,46 +693,63 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -686,46 +774,63 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Change the UI. I'll change it.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -750,46 +855,63 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -814,46 +936,63 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>user stories you figure out and you show me</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -878,46 +1017,63 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>in_progress</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -942,50 +1098,67 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
           <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
         </is>
       </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1010,46 +1183,63 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1074,46 +1264,63 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1138,46 +1345,63 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1202,46 +1426,63 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1266,46 +1507,63 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1330,46 +1588,63 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1394,42 +1669,59 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1454,46 +1746,63 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1518,46 +1827,63 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1582,46 +1908,63 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>I will speak to Lakshmi, plan development plan with model that's it</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1646,49 +1989,66 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:W19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actions'!$A$1:$W$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actions'!$A$1:$W$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1724,90 +1724,106 @@
       <c r="W15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Activity Tracker internal sync-up</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>intelligent-tracker</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Johan</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-01</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
-      <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1832,12 +1848,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1888,7 +1904,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
+          <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1913,12 +1929,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1939,7 +1955,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1967,88 +1983,355 @@
       <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11-intelligent-tracker-08</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Activity Tracker internal sync-up</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-01</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-02</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Adwaith</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>CR section 7.4 Notifications</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-03</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Agree a retention or archival policy for closed periodic closures.</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>CR section 8.6 Sizing</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W19"/>
+  <autoFilter ref="A1:W22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
         <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -67,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -77,6 +82,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1724,106 +1732,90 @@
       <c r="W15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16-lsp-01</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>lsp</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Ayush</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11-intelligent-tracker-02</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Activity Tracker internal sync-up</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>half-day</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
+          <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1848,12 +1840,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1904,7 +1896,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1929,12 +1921,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1955,7 +1947,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1983,352 +1975,380 @@
       <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16-intelligent-tracker-01</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Ayush</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="2" t="inlineStr"/>
-      <c r="V19" s="2" t="inlineStr"/>
-      <c r="W19" s="2" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16-intelligent-tracker-01</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Activity Tracker internal sync-up</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>intelligent-tracker</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Samuel</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-01</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" s="4" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-02</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Adwaith</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
         </is>
       </c>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>CR section 7.4 Notifications</t>
         </is>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Agree a retention or archival policy for closed periodic closures.</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>decide</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="V22" s="5" t="inlineStr">
         <is>
           <t>CR section 8.6 Sizing</t>
         </is>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:W22"/>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -72,16 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1084,575 +1081,575 @@
       <c r="W7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr"/>
-      <c r="V13" s="3" t="inlineStr"/>
-      <c r="W13" s="3" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="3" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1975,376 +1972,376 @@
       <c r="W18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-01</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="4" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-01</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr"/>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="R20" s="5" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
         </is>
       </c>
-      <c r="S20" s="5" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>List of new columns/tables from this CR</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="T20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr">
         <is>
           <t>half-day</t>
         </is>
       </c>
-      <c r="V20" s="5" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
         </is>
       </c>
-      <c r="W20" s="5" t="inlineStr">
+      <c r="W20" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-02</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Adwaith</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R21" s="5" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
         </is>
       </c>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="V21" s="5" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>CR section 7.4 Notifications</t>
         </is>
       </c>
-      <c r="W21" s="5" t="inlineStr">
+      <c r="W21" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Agree a retention or archival policy for closed periodic closures.</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>decide</t>
         </is>
       </c>
-      <c r="R22" s="5" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
         </is>
       </c>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="V22" s="5" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>CR section 8.6 Sizing</t>
         </is>
       </c>
-      <c r="W22" s="5" t="inlineStr">
+      <c r="W22" s="4" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actions'!$A$1:$W$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actions'!$A$1:$W$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,13 +72,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -449,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2055,17 +2058,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-01</t>
+          <t>2026-09-17-unassigned-01</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Code Apps Learning Curriculum Structure Discussion</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2075,44 +2078,48 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Sarathchandra Babu</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+          <t>Or, if you can put a poll in one of these, let's see here.</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>Code Apps - Learning Curriculam Structure Discussion.docx</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr"/>
@@ -2123,232 +2130,325 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>coordinate</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
-        </is>
-      </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
+          <t>Send the poll to the team and collect responses.</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="4" t="inlineStr"/>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>half-day</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
+          <t>D-2026-09-17-02</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16-lsp-02</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-01</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Adwaith</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R21" s="4" t="inlineStr">
-        <is>
-          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
-        </is>
-      </c>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>CR section 7.4 Notifications</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-02</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Adwaith</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>CR section 7.4 Notifications</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Agree a retention or archival policy for closed periodic closures.</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>decide</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="V23" s="5" t="inlineStr">
         <is>
           <t>CR section 8.6 Sizing</t>
         </is>
       </c>
-      <c r="W22" s="4" t="inlineStr">
+      <c r="W23" s="5" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W22"/>
+  <autoFilter ref="A1:W23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Code Apps - Learning Curriculam Structure Discussion.docx</t>
+          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,12 +60,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C0262A"/>
       <sz val="22"/>
     </font>
     <font>
@@ -149,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -157,22 +151,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,13 +178,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,7 +203,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00C0262A"/>
+        <sz val="22"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1030,7 +1035,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot generated 2026-09-17. Regenerated on every run from the Actions sheet; edit items in the Google Sheet, not here.</t>
+          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-17). Edits that should stick belong in the Google Sheet.</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1045,12 @@
           <t>OPEN ITEMS</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>P1 OPEN</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>OVERDUE</t>
         </is>
@@ -1072,30 +1077,37 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="B5" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>3</v>
+      <c r="B5" s="5">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"}))</f>
+        <v/>
+      </c>
+      <c r="C5" s="6">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D5" s="6">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F5" s="5">
+        <f>COUNTIF(Actions!$D$2:$D$5000,"to_verify")</f>
+        <v/>
+      </c>
+      <c r="G5" s="5">
+        <f>COUNTIF(Actions!$D$2:$D$5000,"blocked")</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>COUNTIF(Actions!$D$2:$D$5000,"done")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Open items by owner</t>
         </is>
@@ -1107,193 +1119,228 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>3</v>
+      <c r="C10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>4</v>
+      <c r="C11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>4</v>
+      <c r="C12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>4</v>
+      <c r="C13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>2</v>
+      <c r="C14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Sarathchandra Babu</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0</v>
+      <c r="C15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>17</v>
+      <c r="C16" s="14">
+        <f>SUM(C10:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="14">
+        <f>SUM(D10:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>SUM(E10:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>SUM(F10:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>SUM(G10:G15)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>When is it due</t>
         </is>
@@ -1305,255 +1352,283 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Horizon</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Items</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>13</v>
+      <c r="C24" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&lt;"&amp;TODAY(),Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Due today</t>
         </is>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>0</v>
+      <c r="C25" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,TODAY(),Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Next 7 days</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>0</v>
+      <c r="C26" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY(),Actions!$E$2:$E$5000,"&lt;="&amp;TODAY()+7))</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY(),Actions!$E$2:$E$5000,"&lt;="&amp;TODAY()+7,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>0</v>
+      <c r="C27" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY()+7))</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY()+7,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>No date</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>1</v>
+      <c r="C28" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,""))</f>
+        <v/>
+      </c>
+      <c r="D28" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"",Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>By project</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>0</v>
+      <c r="C33" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B33))</f>
+        <v/>
+      </c>
+      <c r="D33" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B33,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="E33" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B33,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F33" s="11">
+        <f>COUNTIFS(Actions!$F$2:$F$5000,$B33,Actions!$D$2:$D$5000,"done")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>3</v>
+      <c r="C34" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B34))</f>
+        <v/>
+      </c>
+      <c r="D34" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B34,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="E34" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B34,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F34" s="11">
+        <f>COUNTIFS(Actions!$F$2:$F$5000,$B34,Actions!$D$2:$D$5000,"done")</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>0</v>
+      <c r="C35" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B35))</f>
+        <v/>
+      </c>
+      <c r="D35" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B35,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="E35" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B35,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F35" s="11">
+        <f>COUNTIFS(Actions!$F$2:$F$5000,$B35,Actions!$D$2:$D$5000,"done")</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>By status</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Items</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>0</v>
+      <c r="C40" s="12">
+        <f>COUNTIF(Actions!$D$2:$D$5000,$B40)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>in_progress</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>1</v>
+      <c r="C41" s="12">
+        <f>COUNTIF(Actions!$D$2:$D$5000,$B41)</f>
+        <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>18</v>
+      <c r="C42" s="12">
+        <f>COUNTIF(Actions!$D$2:$D$5000,$B42)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>to_verify</t>
         </is>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>0</v>
+      <c r="C43" s="12">
+        <f>COUNTIF(Actions!$D$2:$D$5000,$B43)</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>3</v>
+      <c r="C44" s="12">
+        <f>COUNTIF(Actions!$D$2:$D$5000,$B44)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>rejected</t>
         </is>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>0</v>
+      <c r="C45" s="12">
+        <f>COUNTIF(Actions!$D$2:$D$5000,$B45)</f>
+        <v/>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
@@ -1571,6 +1646,16 @@
     <mergeCell ref="B47:Q48"/>
     <mergeCell ref="D22:Q22"/>
   </mergeCells>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>C5&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>D5&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1611,1837 +1696,1837 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>due</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>next_step</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>unblocker</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>effort</t>
         </is>
       </c>
-      <c r="L1" s="14" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>blocked_by</t>
         </is>
       </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>prerequisites</t>
         </is>
       </c>
-      <c r="N1" s="14" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="O1" s="14" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" s="14" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="Q1" s="14" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>meeting</t>
         </is>
       </c>
-      <c r="R1" s="14" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="S1" s="14" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
       </c>
-      <c r="T1" s="14" t="inlineStr">
+      <c r="T1" s="15" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="U1" s="14" t="inlineStr">
+      <c r="U1" s="15" t="inlineStr">
         <is>
           <t>created</t>
         </is>
       </c>
-      <c r="V1" s="14" t="inlineStr">
+      <c r="V1" s="15" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="W1" s="14" t="inlineStr">
+      <c r="W1" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr"/>
-      <c r="I2" s="15" t="inlineStr"/>
-      <c r="J2" s="15" t="inlineStr"/>
-      <c r="K2" s="16" t="inlineStr"/>
-      <c r="L2" s="15" t="inlineStr"/>
-      <c r="M2" s="15" t="inlineStr"/>
-      <c r="N2" s="15" t="inlineStr"/>
-      <c r="O2" s="15" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="16" t="inlineStr"/>
+      <c r="J2" s="16" t="inlineStr"/>
+      <c r="K2" s="17" t="inlineStr"/>
+      <c r="L2" s="16" t="inlineStr"/>
+      <c r="M2" s="16" t="inlineStr"/>
+      <c r="N2" s="16" t="inlineStr"/>
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
-      <c r="P2" s="15" t="inlineStr"/>
-      <c r="Q2" s="15" t="inlineStr">
+      <c r="P2" s="16" t="inlineStr"/>
+      <c r="Q2" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R2" s="16" t="inlineStr">
+      <c r="R2" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S2" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T2" s="17" t="n"/>
-      <c r="U2" s="17" t="n">
+      <c r="S2" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T2" s="18" t="n"/>
+      <c r="U2" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V2" s="15" t="inlineStr">
+      <c r="V2" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W2" s="15" t="inlineStr">
+      <c r="W2" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr"/>
-      <c r="I3" s="15" t="inlineStr"/>
-      <c r="J3" s="15" t="inlineStr"/>
-      <c r="K3" s="16" t="inlineStr"/>
-      <c r="L3" s="15" t="inlineStr"/>
-      <c r="M3" s="15" t="inlineStr"/>
-      <c r="N3" s="15" t="inlineStr"/>
-      <c r="O3" s="15" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="16" t="inlineStr"/>
+      <c r="J3" s="16" t="inlineStr"/>
+      <c r="K3" s="17" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr"/>
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
-      <c r="P3" s="15" t="inlineStr"/>
-      <c r="Q3" s="15" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr"/>
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R3" s="16" t="inlineStr">
+      <c r="R3" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S3" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T3" s="17" t="n"/>
-      <c r="U3" s="17" t="n">
+      <c r="S3" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T3" s="18" t="n"/>
+      <c r="U3" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V3" s="15" t="inlineStr">
+      <c r="V3" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W3" s="15" t="inlineStr">
+      <c r="W3" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr"/>
-      <c r="I4" s="15" t="inlineStr"/>
-      <c r="J4" s="15" t="inlineStr"/>
-      <c r="K4" s="16" t="inlineStr"/>
-      <c r="L4" s="15" t="inlineStr"/>
-      <c r="M4" s="15" t="inlineStr"/>
-      <c r="N4" s="15" t="inlineStr"/>
-      <c r="O4" s="15" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="16" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="16" t="inlineStr"/>
+      <c r="M4" s="16" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>Change the UI. I'll change it.</t>
         </is>
       </c>
-      <c r="P4" s="15" t="inlineStr"/>
-      <c r="Q4" s="15" t="inlineStr">
+      <c r="P4" s="16" t="inlineStr"/>
+      <c r="Q4" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R4" s="16" t="inlineStr">
+      <c r="R4" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S4" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T4" s="17" t="n"/>
-      <c r="U4" s="17" t="n">
+      <c r="S4" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T4" s="18" t="n"/>
+      <c r="U4" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V4" s="15" t="inlineStr">
+      <c r="V4" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W4" s="15" t="inlineStr">
+      <c r="W4" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="15" t="inlineStr"/>
-      <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="15" t="inlineStr"/>
-      <c r="M5" s="15" t="inlineStr"/>
-      <c r="N5" s="15" t="inlineStr"/>
-      <c r="O5" s="15" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="16" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr"/>
+      <c r="N5" s="16" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr">
         <is>
           <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
-      <c r="P5" s="15" t="inlineStr"/>
-      <c r="Q5" s="15" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R5" s="16" t="inlineStr">
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S5" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n">
+      <c r="S5" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T5" s="18" t="n"/>
+      <c r="U5" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V5" s="15" t="inlineStr">
+      <c r="V5" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W5" s="15" t="inlineStr">
+      <c r="W5" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr"/>
-      <c r="I6" s="15" t="inlineStr"/>
-      <c r="J6" s="15" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
-      <c r="L6" s="15" t="inlineStr"/>
-      <c r="M6" s="15" t="inlineStr"/>
-      <c r="N6" s="15" t="inlineStr"/>
-      <c r="O6" s="15" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr"/>
+      <c r="I6" s="16" t="inlineStr"/>
+      <c r="J6" s="16" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr"/>
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>user stories you figure out and you show me</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr"/>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr"/>
+      <c r="Q6" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R6" s="16" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S6" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T6" s="17" t="n"/>
-      <c r="U6" s="17" t="n">
+      <c r="S6" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T6" s="18" t="n"/>
+      <c r="U6" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V6" s="15" t="inlineStr">
+      <c r="V6" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W6" s="15" t="inlineStr">
+      <c r="W6" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>in_progress</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr"/>
-      <c r="I7" s="15" t="inlineStr"/>
-      <c r="J7" s="15" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr"/>
-      <c r="M7" s="15" t="inlineStr"/>
-      <c r="N7" s="15" t="inlineStr"/>
-      <c r="O7" s="15" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr"/>
+      <c r="I7" s="16" t="inlineStr"/>
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr"/>
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr"/>
-      <c r="Q7" s="15" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R7" s="16" t="inlineStr">
+      <c r="R7" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S7" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T7" s="17" t="n"/>
-      <c r="U7" s="17" t="n">
+      <c r="S7" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T7" s="18" t="n"/>
+      <c r="U7" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="V7" s="15" t="inlineStr">
+      <c r="V7" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W7" s="15" t="inlineStr">
+      <c r="W7" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="E8" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr"/>
-      <c r="I8" s="15" t="inlineStr"/>
-      <c r="J8" s="15" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="15" t="inlineStr"/>
-      <c r="M8" s="15" t="inlineStr"/>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="16" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
         </is>
       </c>
-      <c r="O8" s="15" t="inlineStr">
+      <c r="O8" s="16" t="inlineStr">
         <is>
           <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr"/>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr"/>
+      <c r="Q8" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R8" s="16" t="inlineStr">
+      <c r="R8" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S8" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T8" s="17" t="n"/>
-      <c r="U8" s="17" t="n">
+      <c r="S8" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T8" s="18" t="n"/>
+      <c r="U8" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="V8" s="15" t="inlineStr">
+      <c r="V8" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W8" s="15" t="inlineStr">
+      <c r="W8" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="E9" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr"/>
-      <c r="I9" s="15" t="inlineStr"/>
-      <c r="J9" s="15" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="15" t="inlineStr"/>
-      <c r="M9" s="15" t="inlineStr"/>
-      <c r="N9" s="15" t="inlineStr"/>
-      <c r="O9" s="15" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr"/>
+      <c r="I9" s="16" t="inlineStr"/>
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr"/>
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
-      <c r="P9" s="15" t="inlineStr"/>
-      <c r="Q9" s="15" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr"/>
+      <c r="Q9" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R9" s="16" t="inlineStr">
+      <c r="R9" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S9" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T9" s="17" t="n"/>
-      <c r="U9" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V9" s="15" t="inlineStr">
+      <c r="S9" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T9" s="18" t="n"/>
+      <c r="U9" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V9" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W9" s="15" t="inlineStr">
+      <c r="W9" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E10" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="E10" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr"/>
-      <c r="I10" s="15" t="inlineStr"/>
-      <c r="J10" s="15" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="15" t="inlineStr"/>
-      <c r="M10" s="15" t="inlineStr"/>
-      <c r="N10" s="15" t="inlineStr"/>
-      <c r="O10" s="15" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr"/>
+      <c r="I10" s="16" t="inlineStr"/>
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr"/>
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
-      <c r="P10" s="15" t="inlineStr"/>
-      <c r="Q10" s="15" t="inlineStr">
+      <c r="P10" s="16" t="inlineStr"/>
+      <c r="Q10" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R10" s="16" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S10" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T10" s="17" t="n"/>
-      <c r="U10" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V10" s="15" t="inlineStr">
+      <c r="S10" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T10" s="18" t="n"/>
+      <c r="U10" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V10" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W10" s="15" t="inlineStr">
+      <c r="W10" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E11" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="E11" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr"/>
-      <c r="I11" s="15" t="inlineStr"/>
-      <c r="J11" s="15" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="15" t="inlineStr"/>
-      <c r="M11" s="15" t="inlineStr"/>
-      <c r="N11" s="15" t="inlineStr"/>
-      <c r="O11" s="15" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr"/>
+      <c r="I11" s="16" t="inlineStr"/>
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr"/>
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr"/>
-      <c r="Q11" s="15" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R11" s="16" t="inlineStr">
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S11" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T11" s="17" t="n"/>
-      <c r="U11" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V11" s="15" t="inlineStr">
+      <c r="S11" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T11" s="18" t="n"/>
+      <c r="U11" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V11" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W11" s="15" t="inlineStr">
+      <c r="W11" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="E12" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr"/>
-      <c r="I12" s="15" t="inlineStr"/>
-      <c r="J12" s="15" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="15" t="inlineStr"/>
-      <c r="M12" s="15" t="inlineStr"/>
-      <c r="N12" s="15" t="inlineStr"/>
-      <c r="O12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr"/>
+      <c r="I12" s="16" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr"/>
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
-      <c r="P12" s="15" t="inlineStr"/>
-      <c r="Q12" s="15" t="inlineStr">
+      <c r="P12" s="16" t="inlineStr"/>
+      <c r="Q12" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R12" s="16" t="inlineStr">
+      <c r="R12" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S12" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T12" s="17" t="n"/>
-      <c r="U12" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V12" s="15" t="inlineStr">
+      <c r="S12" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T12" s="18" t="n"/>
+      <c r="U12" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V12" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W12" s="15" t="inlineStr">
+      <c r="W12" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="E13" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr"/>
-      <c r="I13" s="15" t="inlineStr"/>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="15" t="inlineStr"/>
-      <c r="M13" s="15" t="inlineStr"/>
-      <c r="N13" s="15" t="inlineStr"/>
-      <c r="O13" s="15" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr"/>
+      <c r="I13" s="16" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr"/>
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
-      <c r="P13" s="15" t="inlineStr"/>
-      <c r="Q13" s="15" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R13" s="16" t="inlineStr">
+      <c r="R13" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S13" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T13" s="17" t="n"/>
-      <c r="U13" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V13" s="15" t="inlineStr">
+      <c r="S13" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T13" s="18" t="n"/>
+      <c r="U13" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V13" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W13" s="15" t="inlineStr">
+      <c r="W13" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="E14" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr"/>
-      <c r="I14" s="15" t="inlineStr"/>
-      <c r="J14" s="15" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="15" t="inlineStr"/>
-      <c r="M14" s="15" t="inlineStr"/>
-      <c r="N14" s="15" t="inlineStr"/>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr"/>
+      <c r="I14" s="16" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr"/>
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr"/>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="16" t="inlineStr"/>
+      <c r="Q14" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R14" s="16" t="inlineStr">
+      <c r="R14" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S14" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T14" s="17" t="n"/>
-      <c r="U14" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V14" s="15" t="inlineStr">
+      <c r="S14" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T14" s="18" t="n"/>
+      <c r="U14" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V14" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W14" s="15" t="inlineStr">
+      <c r="W14" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr"/>
-      <c r="I15" s="15" t="inlineStr"/>
-      <c r="J15" s="15" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="15" t="inlineStr"/>
-      <c r="M15" s="15" t="inlineStr"/>
-      <c r="N15" s="15" t="inlineStr"/>
-      <c r="O15" s="15" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr"/>
+      <c r="I15" s="16" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr"/>
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
-      <c r="P15" s="15" t="inlineStr"/>
-      <c r="Q15" s="15" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="R15" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S15" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T15" s="17" t="n"/>
-      <c r="U15" s="17" t="n">
+      <c r="S15" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T15" s="18" t="n"/>
+      <c r="U15" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="V15" s="15" t="inlineStr">
+      <c r="V15" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W15" s="15" t="inlineStr">
+      <c r="W15" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr"/>
-      <c r="I16" s="15" t="inlineStr"/>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="15" t="inlineStr"/>
-      <c r="M16" s="15" t="inlineStr"/>
-      <c r="N16" s="15" t="inlineStr"/>
-      <c r="O16" s="15" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr"/>
+      <c r="I16" s="16" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr"/>
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
-      <c r="P16" s="15" t="inlineStr"/>
-      <c r="Q16" s="15" t="inlineStr">
+      <c r="P16" s="16" t="inlineStr"/>
+      <c r="Q16" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R16" s="16" t="inlineStr">
+      <c r="R16" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S16" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T16" s="17" t="n"/>
-      <c r="U16" s="17" t="n">
+      <c r="S16" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T16" s="18" t="n"/>
+      <c r="U16" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V16" s="15" t="inlineStr">
+      <c r="V16" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W16" s="15" t="inlineStr">
+      <c r="W16" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr"/>
-      <c r="I17" s="15" t="inlineStr"/>
-      <c r="J17" s="15" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="15" t="inlineStr"/>
-      <c r="M17" s="15" t="inlineStr"/>
-      <c r="N17" s="15" t="inlineStr"/>
-      <c r="O17" s="15" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr"/>
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
-      <c r="P17" s="15" t="inlineStr"/>
-      <c r="Q17" s="15" t="inlineStr">
+      <c r="P17" s="16" t="inlineStr"/>
+      <c r="Q17" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R17" s="16" t="inlineStr">
+      <c r="R17" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S17" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T17" s="17" t="n"/>
-      <c r="U17" s="17" t="n">
+      <c r="S17" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T17" s="18" t="n"/>
+      <c r="U17" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V17" s="15" t="inlineStr">
+      <c r="V17" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W17" s="15" t="inlineStr">
+      <c r="W17" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr"/>
-      <c r="I18" s="15" t="inlineStr"/>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="15" t="inlineStr"/>
-      <c r="M18" s="15" t="inlineStr"/>
-      <c r="N18" s="15" t="inlineStr"/>
-      <c r="O18" s="15" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr"/>
+      <c r="I18" s="16" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr"/>
+      <c r="O18" s="16" t="inlineStr">
         <is>
           <t>I will speak to Lakshmi, plan development plan with model that's it</t>
         </is>
       </c>
-      <c r="P18" s="15" t="inlineStr"/>
-      <c r="Q18" s="15" t="inlineStr">
+      <c r="P18" s="16" t="inlineStr"/>
+      <c r="Q18" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R18" s="16" t="inlineStr">
+      <c r="R18" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S18" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T18" s="17" t="n"/>
-      <c r="U18" s="17" t="n">
+      <c r="S18" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T18" s="18" t="n"/>
+      <c r="U18" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V18" s="15" t="inlineStr">
+      <c r="V18" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W18" s="15" t="inlineStr">
+      <c r="W18" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E19" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="E19" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr"/>
-      <c r="I19" s="15" t="inlineStr"/>
-      <c r="J19" s="15" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="15" t="inlineStr"/>
-      <c r="M19" s="15" t="inlineStr"/>
-      <c r="N19" s="15" t="inlineStr"/>
-      <c r="O19" s="15" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
-      <c r="P19" s="15" t="inlineStr"/>
-      <c r="Q19" s="15" t="inlineStr">
+      <c r="P19" s="16" t="inlineStr"/>
+      <c r="Q19" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R19" s="16" t="inlineStr">
+      <c r="R19" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S19" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T19" s="17" t="n"/>
-      <c r="U19" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V19" s="15" t="inlineStr">
+      <c r="S19" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T19" s="18" t="n"/>
+      <c r="U19" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V19" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W19" s="15" t="inlineStr">
+      <c r="W19" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Sarathchandra Babu</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>coordinate</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>Send the poll to the team and collect responses.</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="L20" s="15" t="inlineStr"/>
-      <c r="M20" s="15" t="inlineStr"/>
-      <c r="N20" s="15" t="inlineStr"/>
-      <c r="O20" s="15" t="inlineStr">
+      <c r="L20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr"/>
+      <c r="O20" s="16" t="inlineStr">
         <is>
           <t>Or, if you can put a poll in one of these, let's see here.</t>
         </is>
       </c>
-      <c r="P20" s="15" t="inlineStr">
+      <c r="P20" s="16" t="inlineStr">
         <is>
           <t>D-2026-09-17-02</t>
         </is>
       </c>
-      <c r="Q20" s="15" t="inlineStr">
+      <c r="Q20" s="16" t="inlineStr">
         <is>
           <t>Code Apps Learning Curriculum Structure Discussion</t>
         </is>
       </c>
-      <c r="R20" s="16" t="inlineStr">
+      <c r="R20" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S20" s="17" t="n">
+      <c r="S20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="T20" s="17" t="n"/>
-      <c r="U20" s="17" t="n">
+      <c r="T20" s="18" t="n"/>
+      <c r="U20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V20" s="15" t="inlineStr">
+      <c r="V20" s="16" t="inlineStr">
         <is>
           <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
         </is>
       </c>
-      <c r="W20" s="15" t="inlineStr">
+      <c r="W20" s="16" t="inlineStr">
         <is>
           <t>2026-09-17-unassigned-01</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr"/>
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>half-day</t>
         </is>
       </c>
-      <c r="L21" s="15" t="inlineStr"/>
-      <c r="M21" s="15" t="inlineStr">
+      <c r="L21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr">
         <is>
           <t>List of new columns/tables from this CR</t>
         </is>
       </c>
-      <c r="N21" s="15" t="inlineStr"/>
-      <c r="O21" s="15" t="inlineStr">
+      <c r="N21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="inlineStr">
         <is>
           <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
         </is>
       </c>
-      <c r="P21" s="15" t="inlineStr">
+      <c r="P21" s="16" t="inlineStr">
         <is>
           <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
         </is>
       </c>
-      <c r="Q21" s="15" t="inlineStr">
+      <c r="Q21" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="R21" s="16" t="inlineStr">
+      <c r="R21" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S21" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T21" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="U21" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V21" s="15" t="inlineStr">
+      <c r="S21" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T21" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U21" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V21" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="W21" s="15" t="inlineStr">
+      <c r="W21" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-01</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Adwaith</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr"/>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L22" s="15" t="inlineStr"/>
-      <c r="M22" s="15" t="inlineStr"/>
-      <c r="N22" s="15" t="inlineStr"/>
-      <c r="O22" s="15" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr"/>
+      <c r="O22" s="16" t="inlineStr">
         <is>
           <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
         </is>
       </c>
-      <c r="P22" s="15" t="inlineStr">
+      <c r="P22" s="16" t="inlineStr">
         <is>
           <t>CR section 7.4 Notifications</t>
         </is>
       </c>
-      <c r="Q22" s="15" t="inlineStr">
+      <c r="Q22" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="R22" s="16" t="inlineStr">
+      <c r="R22" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S22" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T22" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="U22" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V22" s="15" t="inlineStr">
+      <c r="S22" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T22" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U22" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V22" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="W22" s="15" t="inlineStr">
+      <c r="W22" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-02</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>decide</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr"/>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L23" s="15" t="inlineStr"/>
-      <c r="M23" s="15" t="inlineStr"/>
-      <c r="N23" s="15" t="inlineStr"/>
-      <c r="O23" s="15" t="inlineStr">
+      <c r="L23" s="16" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr"/>
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>Agree a retention or archival policy for closed periodic closures.</t>
         </is>
       </c>
-      <c r="P23" s="15" t="inlineStr">
+      <c r="P23" s="16" t="inlineStr">
         <is>
           <t>CR section 8.6 Sizing</t>
         </is>
       </c>
-      <c r="Q23" s="15" t="inlineStr">
+      <c r="Q23" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="R23" s="16" t="inlineStr">
+      <c r="R23" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S23" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T23" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="U23" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V23" s="15" t="inlineStr">
+      <c r="S23" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="T23" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U23" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V23" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="W23" s="15" t="inlineStr">
+      <c r="W23" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>
@@ -3449,40 +3534,40 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D5000">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="1">
       <formula>$D2="done"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="2">
       <formula>$D2="to_verify"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>$D2="blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="4">
       <formula>$D2="in_progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C5000">
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="5">
       <formula>AND($C2="P1",NOT(OR($D2="done",$D2="rejected")))</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="6">
       <formula>AND($C2="P2",NOT(OR($D2="done",$D2="rejected")))</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND($C2="P3",NOT(OR($D2="done",$D2="rejected")))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E5000">
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="8" dxfId="8">
       <formula>AND($E2&lt;&gt;"",$E2&lt;TODAY(),NOT(OR($D2="done",$D2="rejected")))</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
+    <cfRule type="expression" priority="9" dxfId="9">
       <formula>AND($E2&lt;&gt;"",$E2=TODAY(),NOT(OR($D2="done",$D2="rejected")))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:W5000">
-    <cfRule type="expression" priority="10" dxfId="9">
+    <cfRule type="expression" priority="10" dxfId="10">
       <formula>OR($D2="done",$D2="rejected")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -683,9 +683,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:W23" headerRowCount="1">
-  <autoFilter ref="A1:W23"/>
-  <tableColumns count="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X23" headerRowCount="1">
+  <autoFilter ref="A1:X23"/>
+  <tableColumns count="24">
     <tableColumn id="1" name="task"/>
     <tableColumn id="2" name="owner"/>
     <tableColumn id="3" name="priority"/>
@@ -702,13 +702,14 @@
     <tableColumn id="14" name="notes"/>
     <tableColumn id="15" name="evidence"/>
     <tableColumn id="16" name="basis"/>
-    <tableColumn id="17" name="meeting"/>
-    <tableColumn id="18" name="origin"/>
-    <tableColumn id="19" name="updated"/>
-    <tableColumn id="20" name="closed"/>
-    <tableColumn id="21" name="created"/>
-    <tableColumn id="22" name="source"/>
-    <tableColumn id="23" name="id"/>
+    <tableColumn id="17" name="flags"/>
+    <tableColumn id="18" name="meeting"/>
+    <tableColumn id="19" name="origin"/>
+    <tableColumn id="20" name="updated"/>
+    <tableColumn id="21" name="closed"/>
+    <tableColumn id="22" name="created"/>
+    <tableColumn id="23" name="source"/>
+    <tableColumn id="24" name="id"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1667,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1686,13 +1687,14 @@
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
     <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1778,35 +1780,40 @@
       </c>
       <c r="Q1" s="15" t="inlineStr">
         <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="R1" s="15" t="inlineStr">
+        <is>
           <t>meeting</t>
         </is>
       </c>
-      <c r="R1" s="15" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="S1" s="15" t="inlineStr">
+      <c r="T1" s="15" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
       </c>
-      <c r="T1" s="15" t="inlineStr">
+      <c r="U1" s="15" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="U1" s="15" t="inlineStr">
+      <c r="V1" s="15" t="inlineStr">
         <is>
           <t>created</t>
         </is>
       </c>
-      <c r="V1" s="15" t="inlineStr">
+      <c r="W1" s="15" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="W1" s="15" t="inlineStr">
+      <c r="X1" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -1859,29 +1866,30 @@
         </is>
       </c>
       <c r="P2" s="16" t="inlineStr"/>
-      <c r="Q2" s="16" t="inlineStr">
+      <c r="Q2" s="16" t="inlineStr"/>
+      <c r="R2" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R2" s="17" t="inlineStr">
+      <c r="S2" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S2" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T2" s="18" t="n"/>
-      <c r="U2" s="18" t="n">
+      <c r="T2" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U2" s="18" t="n"/>
+      <c r="V2" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V2" s="16" t="inlineStr">
+      <c r="W2" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W2" s="16" t="inlineStr">
+      <c r="X2" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-01</t>
         </is>
@@ -1934,29 +1942,30 @@
         </is>
       </c>
       <c r="P3" s="16" t="inlineStr"/>
-      <c r="Q3" s="16" t="inlineStr">
+      <c r="Q3" s="16" t="inlineStr"/>
+      <c r="R3" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="S3" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S3" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T3" s="18" t="n"/>
-      <c r="U3" s="18" t="n">
+      <c r="T3" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U3" s="18" t="n"/>
+      <c r="V3" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V3" s="16" t="inlineStr">
+      <c r="W3" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W3" s="16" t="inlineStr">
+      <c r="X3" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-04</t>
         </is>
@@ -2009,29 +2018,30 @@
         </is>
       </c>
       <c r="P4" s="16" t="inlineStr"/>
-      <c r="Q4" s="16" t="inlineStr">
+      <c r="Q4" s="16" t="inlineStr"/>
+      <c r="R4" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="S4" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S4" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T4" s="18" t="n"/>
-      <c r="U4" s="18" t="n">
+      <c r="T4" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U4" s="18" t="n"/>
+      <c r="V4" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V4" s="16" t="inlineStr">
+      <c r="W4" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W4" s="16" t="inlineStr">
+      <c r="X4" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-05</t>
         </is>
@@ -2084,29 +2094,30 @@
         </is>
       </c>
       <c r="P5" s="16" t="inlineStr"/>
-      <c r="Q5" s="16" t="inlineStr">
+      <c r="Q5" s="16" t="inlineStr"/>
+      <c r="R5" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="S5" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S5" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T5" s="18" t="n"/>
-      <c r="U5" s="18" t="n">
+      <c r="T5" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U5" s="18" t="n"/>
+      <c r="V5" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V5" s="16" t="inlineStr">
+      <c r="W5" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W5" s="16" t="inlineStr">
+      <c r="X5" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-06</t>
         </is>
@@ -2159,29 +2170,30 @@
         </is>
       </c>
       <c r="P6" s="16" t="inlineStr"/>
-      <c r="Q6" s="16" t="inlineStr">
+      <c r="Q6" s="16" t="inlineStr"/>
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="S6" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S6" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T6" s="18" t="n"/>
-      <c r="U6" s="18" t="n">
+      <c r="T6" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U6" s="18" t="n"/>
+      <c r="V6" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V6" s="16" t="inlineStr">
+      <c r="W6" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W6" s="16" t="inlineStr">
+      <c r="X6" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-07</t>
         </is>
@@ -2234,29 +2246,30 @@
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr">
+      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="R7" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="S7" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S7" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T7" s="18" t="n"/>
-      <c r="U7" s="18" t="n">
+      <c r="T7" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U7" s="18" t="n"/>
+      <c r="V7" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="V7" s="16" t="inlineStr">
+      <c r="W7" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W7" s="16" t="inlineStr">
+      <c r="X7" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-01</t>
         </is>
@@ -2313,29 +2326,30 @@
         </is>
       </c>
       <c r="P8" s="16" t="inlineStr"/>
-      <c r="Q8" s="16" t="inlineStr">
+      <c r="Q8" s="16" t="inlineStr"/>
+      <c r="R8" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="S8" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S8" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T8" s="18" t="n"/>
-      <c r="U8" s="18" t="n">
+      <c r="T8" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U8" s="18" t="n"/>
+      <c r="V8" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="V8" s="16" t="inlineStr">
+      <c r="W8" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W8" s="16" t="inlineStr">
+      <c r="X8" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-02</t>
         </is>
@@ -2388,29 +2402,30 @@
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr"/>
-      <c r="Q9" s="16" t="inlineStr">
+      <c r="Q9" s="16" t="inlineStr"/>
+      <c r="R9" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="S9" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S9" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T9" s="18" t="n"/>
-      <c r="U9" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V9" s="16" t="inlineStr">
+      <c r="T9" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U9" s="18" t="n"/>
+      <c r="V9" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W9" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W9" s="16" t="inlineStr">
+      <c r="X9" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-02</t>
         </is>
@@ -2463,29 +2478,30 @@
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr"/>
-      <c r="Q10" s="16" t="inlineStr">
+      <c r="Q10" s="16" t="inlineStr"/>
+      <c r="R10" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="S10" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S10" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T10" s="18" t="n"/>
-      <c r="U10" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V10" s="16" t="inlineStr">
+      <c r="T10" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U10" s="18" t="n"/>
+      <c r="V10" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W10" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W10" s="16" t="inlineStr">
+      <c r="X10" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-03</t>
         </is>
@@ -2538,29 +2554,30 @@
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr"/>
-      <c r="Q11" s="16" t="inlineStr">
+      <c r="Q11" s="16" t="inlineStr"/>
+      <c r="R11" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="S11" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S11" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T11" s="18" t="n"/>
-      <c r="U11" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V11" s="16" t="inlineStr">
+      <c r="T11" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U11" s="18" t="n"/>
+      <c r="V11" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W11" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W11" s="16" t="inlineStr">
+      <c r="X11" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-04</t>
         </is>
@@ -2613,29 +2630,30 @@
         </is>
       </c>
       <c r="P12" s="16" t="inlineStr"/>
-      <c r="Q12" s="16" t="inlineStr">
+      <c r="Q12" s="16" t="inlineStr"/>
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="S12" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S12" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T12" s="18" t="n"/>
-      <c r="U12" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V12" s="16" t="inlineStr">
+      <c r="T12" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U12" s="18" t="n"/>
+      <c r="V12" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W12" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W12" s="16" t="inlineStr">
+      <c r="X12" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-05</t>
         </is>
@@ -2688,29 +2706,30 @@
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr">
+      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="R13" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="S13" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S13" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T13" s="18" t="n"/>
-      <c r="U13" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V13" s="16" t="inlineStr">
+      <c r="T13" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U13" s="18" t="n"/>
+      <c r="V13" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W13" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W13" s="16" t="inlineStr">
+      <c r="X13" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-06</t>
         </is>
@@ -2763,29 +2782,30 @@
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr"/>
-      <c r="Q14" s="16" t="inlineStr">
+      <c r="Q14" s="16" t="inlineStr"/>
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="S14" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S14" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T14" s="18" t="n"/>
-      <c r="U14" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V14" s="16" t="inlineStr">
+      <c r="T14" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U14" s="18" t="n"/>
+      <c r="V14" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W14" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W14" s="16" t="inlineStr">
+      <c r="X14" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-07</t>
         </is>
@@ -2836,29 +2856,30 @@
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr"/>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="Q15" s="16" t="inlineStr"/>
+      <c r="R15" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="S15" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S15" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T15" s="18" t="n"/>
-      <c r="U15" s="18" t="n">
+      <c r="T15" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U15" s="18" t="n"/>
+      <c r="V15" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="V15" s="16" t="inlineStr">
+      <c r="W15" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W15" s="16" t="inlineStr">
+      <c r="X15" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-03</t>
         </is>
@@ -2911,29 +2932,30 @@
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr"/>
-      <c r="Q16" s="16" t="inlineStr">
+      <c r="Q16" s="16" t="inlineStr"/>
+      <c r="R16" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="S16" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S16" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T16" s="18" t="n"/>
-      <c r="U16" s="18" t="n">
+      <c r="T16" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U16" s="18" t="n"/>
+      <c r="V16" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V16" s="16" t="inlineStr">
+      <c r="W16" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W16" s="16" t="inlineStr">
+      <c r="X16" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-02</t>
         </is>
@@ -2986,29 +3008,30 @@
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr"/>
-      <c r="Q17" s="16" t="inlineStr">
+      <c r="Q17" s="16" t="inlineStr"/>
+      <c r="R17" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="S17" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S17" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T17" s="18" t="n"/>
-      <c r="U17" s="18" t="n">
+      <c r="T17" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U17" s="18" t="n"/>
+      <c r="V17" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V17" s="16" t="inlineStr">
+      <c r="W17" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W17" s="16" t="inlineStr">
+      <c r="X17" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-03</t>
         </is>
@@ -3061,29 +3084,30 @@
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
-      <c r="Q18" s="16" t="inlineStr">
+      <c r="Q18" s="16" t="inlineStr"/>
+      <c r="R18" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="S18" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S18" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T18" s="18" t="n"/>
-      <c r="U18" s="18" t="n">
+      <c r="T18" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U18" s="18" t="n"/>
+      <c r="V18" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="V18" s="16" t="inlineStr">
+      <c r="W18" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W18" s="16" t="inlineStr">
+      <c r="X18" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-08</t>
         </is>
@@ -3136,29 +3160,30 @@
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr"/>
-      <c r="Q19" s="16" t="inlineStr">
+      <c r="Q19" s="16" t="inlineStr"/>
+      <c r="R19" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="R19" s="17" t="inlineStr">
+      <c r="S19" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S19" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T19" s="18" t="n"/>
-      <c r="U19" s="18" t="n">
-        <v>46281</v>
-      </c>
-      <c r="V19" s="16" t="inlineStr">
+      <c r="T19" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U19" s="18" t="n"/>
+      <c r="V19" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W19" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="W19" s="16" t="inlineStr">
+      <c r="X19" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-01</t>
         </is>
@@ -3227,29 +3252,30 @@
           <t>D-2026-09-17-02</t>
         </is>
       </c>
-      <c r="Q20" s="16" t="inlineStr">
+      <c r="Q20" s="16" t="inlineStr"/>
+      <c r="R20" s="16" t="inlineStr">
         <is>
           <t>Code Apps Learning Curriculum Structure Discussion</t>
         </is>
       </c>
-      <c r="R20" s="17" t="inlineStr">
+      <c r="S20" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S20" s="18" t="n">
+      <c r="T20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="T20" s="18" t="n"/>
-      <c r="U20" s="18" t="n">
+      <c r="U20" s="18" t="n"/>
+      <c r="V20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V20" s="16" t="inlineStr">
+      <c r="W20" s="16" t="inlineStr">
         <is>
           <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
         </is>
       </c>
-      <c r="W20" s="16" t="inlineStr">
+      <c r="X20" s="16" t="inlineStr">
         <is>
           <t>2026-09-17-unassigned-01</t>
         </is>
@@ -3320,31 +3346,32 @@
           <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
         </is>
       </c>
-      <c r="Q21" s="16" t="inlineStr">
+      <c r="Q21" s="16" t="inlineStr"/>
+      <c r="R21" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="R21" s="17" t="inlineStr">
+      <c r="S21" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S21" s="18" t="n">
-        <v>46281</v>
-      </c>
       <c r="T21" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="U21" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="V21" s="16" t="inlineStr">
+      <c r="V21" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W21" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="W21" s="16" t="inlineStr">
+      <c r="X21" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-01</t>
         </is>
@@ -3411,31 +3438,32 @@
           <t>CR section 7.4 Notifications</t>
         </is>
       </c>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="Q22" s="16" t="inlineStr"/>
+      <c r="R22" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="R22" s="17" t="inlineStr">
+      <c r="S22" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S22" s="18" t="n">
-        <v>46281</v>
-      </c>
       <c r="T22" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="U22" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="V22" s="16" t="inlineStr">
+      <c r="V22" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W22" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="W22" s="16" t="inlineStr">
+      <c r="X22" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-02</t>
         </is>
@@ -3502,31 +3530,32 @@
           <t>CR section 8.6 Sizing</t>
         </is>
       </c>
-      <c r="Q23" s="16" t="inlineStr">
+      <c r="Q23" s="16" t="inlineStr"/>
+      <c r="R23" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="R23" s="17" t="inlineStr">
+      <c r="S23" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="S23" s="18" t="n">
-        <v>46281</v>
-      </c>
       <c r="T23" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="U23" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="V23" s="16" t="inlineStr">
+      <c r="V23" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W23" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="W23" s="16" t="inlineStr">
+      <c r="X23" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>
@@ -3566,8 +3595,13 @@
       <formula>AND($E2&lt;&gt;"",$E2=TODAY(),NOT(OR($D2="done",$D2="rejected")))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:W5000">
-    <cfRule type="expression" priority="10" dxfId="10">
+  <conditionalFormatting sqref="Q2:Q5000">
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:X5000">
+    <cfRule type="expression" priority="11" dxfId="10">
       <formula>OR($D2="done",$D2="rejected")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3584,7 +3618,7 @@
     <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown effort" error="Pick one of: 15m, 1h, half-day, day+, unknown" type="list">
       <formula1>"15m,1h,half-day,day+,unknown"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown origin" error="Pick one of: planned, unplanned" type="list">
+    <dataValidation sqref="S2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown origin" error="Pick one of: planned, unplanned" type="list">
       <formula1>"planned,unplanned"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -438,12 +438,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$15</f>
+              <f>'Dashboard'!$B$10:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$10:$C$15</f>
+              <f>'Dashboard'!$C$10:$C$14</f>
             </numRef>
           </val>
         </ser>
@@ -468,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$15</f>
+              <f>'Dashboard'!$B$10:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$10:$D$15</f>
+              <f>'Dashboard'!$D$10:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -498,12 +498,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$15</f>
+              <f>'Dashboard'!$B$10:$B$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$10:$E$15</f>
+              <f>'Dashboard'!$E$10:$E$14</f>
             </numRef>
           </val>
         </ser>
@@ -637,7 +637,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2340000"/>
+    <ext cx="5760000" cy="2142000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1073,25 +1073,25 @@
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="B5" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1141,23 +1141,23 @@
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>0</v>
@@ -1176,20 +1176,20 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>1</v>
@@ -1198,98 +1198,76 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="10" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Sarathchandra Babu</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
+      <c r="E15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>17</v>
+      <c r="F15" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -1328,10 +1306,10 @@
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1341,7 +1319,7 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>0</v>
@@ -1427,16 +1405,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -1465,7 +1443,7 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>0</v>
@@ -1474,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1513,7 +1491,7 @@
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1523,7 +1501,7 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1533,7 +1511,7 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1543,7 +1521,7 @@
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -1730,12 +1708,12 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Sign off on the reviewed database design after today's walkthrough.</t>
+          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -1745,11 +1723,11 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F2" s="15" t="inlineStr">
         <is>
@@ -1767,10 +1745,14 @@
       <c r="K2" s="16" t="inlineStr"/>
       <c r="L2" s="15" t="inlineStr"/>
       <c r="M2" s="15" t="inlineStr"/>
-      <c r="N2" s="15" t="inlineStr"/>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
+        </is>
+      </c>
       <c r="O2" s="15" t="inlineStr">
         <is>
-          <t>I will be signing off on the Debi after the review</t>
+          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
       <c r="P2" s="15" t="inlineStr"/>
@@ -1785,32 +1767,32 @@
         </is>
       </c>
       <c r="S2" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T2" s="17" t="n"/>
       <c r="U2" s="17" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="V2" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W2" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-01</t>
+          <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Work with Ashwini on the overall workflow solution design document.</t>
+          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
@@ -1820,11 +1802,11 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>to_verify</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
@@ -1845,7 +1827,7 @@
       <c r="N3" s="15" t="inlineStr"/>
       <c r="O3" s="15" t="inlineStr">
         <is>
-          <t>Lakshmi and I will be working on the proper workflow solution design</t>
+          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
       <c r="P3" s="15" t="inlineStr"/>
@@ -1860,32 +1842,32 @@
         </is>
       </c>
       <c r="S3" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T3" s="17" t="n"/>
       <c r="U3" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="V3" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W3" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-04</t>
+          <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
+          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -1895,11 +1877,11 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>to_verify</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
@@ -1920,7 +1902,7 @@
       <c r="N4" s="15" t="inlineStr"/>
       <c r="O4" s="15" t="inlineStr">
         <is>
-          <t>Change the UI. I'll change it.</t>
+          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
       <c r="P4" s="15" t="inlineStr"/>
@@ -1935,32 +1917,32 @@
         </is>
       </c>
       <c r="S4" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T4" s="17" t="n"/>
       <c r="U4" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="V4" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W4" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-05</t>
+          <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
+          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -1970,11 +1952,11 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>to_verify</t>
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
@@ -1995,7 +1977,7 @@
       <c r="N5" s="15" t="inlineStr"/>
       <c r="O5" s="15" t="inlineStr">
         <is>
-          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
+          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
       <c r="P5" s="15" t="inlineStr"/>
@@ -2010,32 +1992,32 @@
         </is>
       </c>
       <c r="S5" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T5" s="17" t="n"/>
       <c r="U5" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="V5" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W5" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-06</t>
+          <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
+          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -2045,11 +2027,11 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="E6" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
@@ -2070,7 +2052,7 @@
       <c r="N6" s="15" t="inlineStr"/>
       <c r="O6" s="15" t="inlineStr">
         <is>
-          <t>user stories you figure out and you show me</t>
+          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
       <c r="P6" s="15" t="inlineStr"/>
@@ -2085,32 +2067,32 @@
         </is>
       </c>
       <c r="S6" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T6" s="17" t="n"/>
       <c r="U6" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="V6" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W6" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-07</t>
+          <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
+          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -2120,12 +2102,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>46280</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n"/>
       <c r="F7" s="15" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -2145,7 +2125,7 @@
       <c r="N7" s="15" t="inlineStr"/>
       <c r="O7" s="15" t="inlineStr">
         <is>
-          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
+          <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
       <c r="P7" s="15" t="inlineStr"/>
@@ -2173,24 +2153,24 @@
       </c>
       <c r="W7" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-01</t>
+          <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -2199,7 +2179,7 @@
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
@@ -2217,14 +2197,10 @@
       <c r="K8" s="16" t="inlineStr"/>
       <c r="L8" s="15" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
-        </is>
-      </c>
+      <c r="N8" s="15" t="inlineStr"/>
       <c r="O8" s="15" t="inlineStr">
         <is>
-          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
         </is>
       </c>
       <c r="P8" s="15" t="inlineStr"/>
@@ -2243,38 +2219,38 @@
       </c>
       <c r="T8" s="17" t="n"/>
       <c r="U8" s="17" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="V8" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W8" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-02</t>
+          <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
+          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>to_verify</t>
         </is>
       </c>
       <c r="E9" s="17" t="n">
@@ -2299,7 +2275,7 @@
       <c r="N9" s="15" t="inlineStr"/>
       <c r="O9" s="15" t="inlineStr">
         <is>
-          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
       <c r="P9" s="15" t="inlineStr"/>
@@ -2314,7 +2290,7 @@
         </is>
       </c>
       <c r="S9" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T9" s="17" t="n"/>
       <c r="U9" s="17" t="n">
@@ -2327,19 +2303,19 @@
       </c>
       <c r="W9" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
+          <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -2349,11 +2325,11 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
@@ -2374,7 +2350,7 @@
       <c r="N10" s="15" t="inlineStr"/>
       <c r="O10" s="15" t="inlineStr">
         <is>
-          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
+          <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
       <c r="P10" s="15" t="inlineStr"/>
@@ -2389,27 +2365,29 @@
         </is>
       </c>
       <c r="S10" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T10" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T10" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U10" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="V10" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W10" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-03</t>
+          <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
+          <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -2424,11 +2402,11 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
@@ -2449,7 +2427,7 @@
       <c r="N11" s="15" t="inlineStr"/>
       <c r="O11" s="15" t="inlineStr">
         <is>
-          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
+          <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
       <c r="P11" s="15" t="inlineStr"/>
@@ -2464,32 +2442,34 @@
         </is>
       </c>
       <c r="S11" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T11" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T11" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U11" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="V11" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W11" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-04</t>
+          <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
+          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -2499,11 +2479,11 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
@@ -2524,7 +2504,7 @@
       <c r="N12" s="15" t="inlineStr"/>
       <c r="O12" s="15" t="inlineStr">
         <is>
-          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
+          <t>Change the UI. I'll change it.</t>
         </is>
       </c>
       <c r="P12" s="15" t="inlineStr"/>
@@ -2539,32 +2519,34 @@
         </is>
       </c>
       <c r="S12" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T12" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T12" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U12" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="V12" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W12" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-05</t>
+          <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
+          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -2574,11 +2556,11 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
@@ -2599,7 +2581,7 @@
       <c r="N13" s="15" t="inlineStr"/>
       <c r="O13" s="15" t="inlineStr">
         <is>
-          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
+          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
       <c r="P13" s="15" t="inlineStr"/>
@@ -2614,32 +2596,34 @@
         </is>
       </c>
       <c r="S13" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T13" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T13" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U13" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="V13" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W13" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-06</t>
+          <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
+          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -2649,11 +2633,11 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
@@ -2674,7 +2658,7 @@
       <c r="N14" s="15" t="inlineStr"/>
       <c r="O14" s="15" t="inlineStr">
         <is>
-          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+          <t>user stories you figure out and you show me</t>
         </is>
       </c>
       <c r="P14" s="15" t="inlineStr"/>
@@ -2689,32 +2673,34 @@
         </is>
       </c>
       <c r="S14" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T14" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U14" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="V14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-07</t>
+          <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
+          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -2724,10 +2710,12 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>46280</v>
+      </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -2747,7 +2735,7 @@
       <c r="N15" s="15" t="inlineStr"/>
       <c r="O15" s="15" t="inlineStr">
         <is>
-          <t>Yeah, that we will show you on the website.</t>
+          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
       <c r="P15" s="15" t="inlineStr"/>
@@ -2762,9 +2750,11 @@
         </is>
       </c>
       <c r="S15" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T15" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T15" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U15" s="17" t="n">
         <v>46280</v>
       </c>
@@ -2775,33 +2765,33 @@
       </c>
       <c r="W15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-03</t>
+          <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
@@ -2822,7 +2812,7 @@
       <c r="N16" s="15" t="inlineStr"/>
       <c r="O16" s="15" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
       <c r="P16" s="15" t="inlineStr"/>
@@ -2837,46 +2827,48 @@
         </is>
       </c>
       <c r="S16" s="17" t="n">
+        <v>46282</v>
+      </c>
+      <c r="T16" s="17" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U16" s="17" t="n">
         <v>46281</v>
       </c>
-      <c r="T16" s="17" t="n"/>
-      <c r="U16" s="17" t="n">
-        <v>46276</v>
-      </c>
       <c r="V16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W16" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
@@ -2897,7 +2889,7 @@
       <c r="N17" s="15" t="inlineStr"/>
       <c r="O17" s="15" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
       <c r="P17" s="15" t="inlineStr"/>
@@ -2912,27 +2904,29 @@
         </is>
       </c>
       <c r="S17" s="17" t="n">
+        <v>46282</v>
+      </c>
+      <c r="T17" s="17" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U17" s="17" t="n">
         <v>46281</v>
       </c>
-      <c r="T17" s="17" t="n"/>
-      <c r="U17" s="17" t="n">
-        <v>46276</v>
-      </c>
       <c r="V17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
@@ -2942,43 +2936,61 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>46276</v>
-      </c>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n"/>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>lsp</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="inlineStr"/>
-      <c r="I18" s="15" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
       <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
       <c r="L18" s="15" t="inlineStr"/>
-      <c r="M18" s="15" t="inlineStr"/>
+      <c r="M18" s="15" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
       <c r="N18" s="15" t="inlineStr"/>
       <c r="O18" s="15" t="inlineStr">
         <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
-        </is>
-      </c>
-      <c r="P18" s="15" t="inlineStr"/>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
       <c r="Q18" s="15" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
       <c r="R18" s="16" t="inlineStr">
@@ -2989,30 +3001,32 @@
       <c r="S18" s="17" t="n">
         <v>46281</v>
       </c>
-      <c r="T18" s="17" t="n"/>
+      <c r="T18" s="17" t="n">
+        <v>46281</v>
+      </c>
       <c r="U18" s="17" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="V18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
       <c r="W18" s="15" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
+          <t>2026-09-16-lsp-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -3022,11 +3036,11 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
@@ -3047,7 +3061,7 @@
       <c r="N19" s="15" t="inlineStr"/>
       <c r="O19" s="15" t="inlineStr">
         <is>
-          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
       <c r="P19" s="15" t="inlineStr"/>
@@ -3062,32 +3076,34 @@
         </is>
       </c>
       <c r="S19" s="17" t="n">
-        <v>46281</v>
-      </c>
-      <c r="T19" s="17" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U19" s="17" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="V19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-01</t>
+          <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Sarathchandra Babu</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -3097,54 +3113,38 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>coordinate</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Send the poll to the team and collect responses.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr"/>
+      <c r="I20" s="15" t="inlineStr"/>
       <c r="J20" s="15" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K20" s="16" t="inlineStr"/>
       <c r="L20" s="15" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
       <c r="N20" s="15" t="inlineStr"/>
       <c r="O20" s="15" t="inlineStr">
         <is>
-          <t>Or, if you can put a poll in one of these, let's see here.</t>
-        </is>
-      </c>
-      <c r="P20" s="15" t="inlineStr">
-        <is>
-          <t>D-2026-09-17-02</t>
-        </is>
-      </c>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="inlineStr"/>
       <c r="Q20" s="15" t="inlineStr">
         <is>
-          <t>Code Apps Learning Curriculum Structure Discussion</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="R20" s="16" t="inlineStr">
@@ -3155,35 +3155,37 @@
       <c r="S20" s="17" t="n">
         <v>46282</v>
       </c>
-      <c r="T20" s="17" t="n"/>
+      <c r="T20" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="U20" s="17" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="V20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="W20" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17-unassigned-01</t>
+          <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Sarathchandra Babu</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
@@ -3191,10 +3193,12 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E21" s="17" t="n"/>
+      <c r="E21" s="17" t="n">
+        <v>46282</v>
+      </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -3204,40 +3208,36 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>coordinate</t>
         </is>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+          <t>Send the poll to the team and collect responses.</t>
         </is>
       </c>
       <c r="J21" s="15" t="inlineStr"/>
       <c r="K21" s="16" t="inlineStr">
         <is>
-          <t>half-day</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr"/>
-      <c r="M21" s="15" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
+      <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="15" t="inlineStr"/>
       <c r="O21" s="15" t="inlineStr">
         <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+          <t>Or, if you can put a poll in one of these, let's see here.</t>
         </is>
       </c>
       <c r="P21" s="15" t="inlineStr">
         <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+          <t>D-2026-09-17-02</t>
         </is>
       </c>
       <c r="Q21" s="15" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Code Apps Learning Curriculum Structure Discussion</t>
         </is>
       </c>
       <c r="R21" s="16" t="inlineStr">
@@ -3246,22 +3246,22 @@
         </is>
       </c>
       <c r="S21" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="T21" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="U21" s="17" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="V21" s="15" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
         </is>
       </c>
       <c r="W21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-01</t>
+          <t>2026-09-17-unassigned-01</t>
         </is>
       </c>
     </row>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -148,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -177,22 +172,19 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -420,6 +412,157 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Open items by owner and priority</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!C9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1C5CAB"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$C$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!D9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="5598E7"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$D$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!E9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="B7D3F6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$E$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Open items by due horizon</a:t>
             </a:r>
           </a:p>
@@ -496,10 +639,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2520000"/>
+    <ext cx="5760000" cy="1944000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -514,12 +657,34 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2520000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X23" headerRowCount="1">
-  <autoFilter ref="A1:X23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X24" headerRowCount="1">
+  <autoFilter ref="A1:X24"/>
   <tableColumns count="24">
     <tableColumn id="1" name="task"/>
     <tableColumn id="2" name="owner"/>
@@ -989,33 +1154,53 @@
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>No open items</t>
-        </is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B10,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <f>SUM(C10:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <f>SUM(D10:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <f>SUM(E10:E10)</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="14">
         <f>SUM(F10:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="14">
         <f>SUM(G10:G10)</f>
         <v/>
       </c>
@@ -1050,76 +1235,76 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&lt;"&amp;TODAY(),Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Due today</t>
         </is>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,TODAY()))</f>
         <v/>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,TODAY(),Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Next 7 days</t>
         </is>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY(),Actions!$E$2:$E$5000,"&lt;="&amp;TODAY()+7))</f>
         <v/>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY(),Actions!$E$2:$E$5000,"&lt;="&amp;TODAY()+7,Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY()+7))</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"&gt;"&amp;TODAY()+7,Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>No date</t>
         </is>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,""))</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$E$2:$E$5000,"",Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
@@ -1159,70 +1344,70 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B33))</f>
         <v/>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B33,Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B33,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="11">
         <f>COUNTIFS(Actions!$F$2:$F$5000,$B33,Actions!$D$2:$D$5000,"done")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B34))</f>
         <v/>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B34,Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B34,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="11">
         <f>COUNTIFS(Actions!$F$2:$F$5000,$B34,Actions!$D$2:$D$5000,"done")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="12">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B35))</f>
         <v/>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B35,Actions!$C$2:$C$5000,"P1"))</f>
         <v/>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="11">
         <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$F$2:$F$5000,$B35,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="11">
         <f>COUNTIFS(Actions!$F$2:$F$5000,$B35,Actions!$D$2:$D$5000,"done")</f>
         <v/>
       </c>
@@ -1247,67 +1432,67 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="12">
         <f>COUNTIF(Actions!$D$2:$D$5000,$B40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>in_progress</t>
         </is>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="12">
         <f>COUNTIF(Actions!$D$2:$D$5000,$B41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="12">
         <f>COUNTIF(Actions!$D$2:$D$5000,$B42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>to_verify</t>
         </is>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="12">
         <f>COUNTIF(Actions!$D$2:$D$5000,$B43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="12">
         <f>COUNTIF(Actions!$D$2:$D$5000,$B44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>rejected</t>
         </is>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="12">
         <f>COUNTIF(Actions!$D$2:$D$5000,$B45)</f>
         <v/>
       </c>
@@ -1348,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1378,1902 +1563,1998 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>task</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>due</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>next_step</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>unblocker</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>effort</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>blocked_by</t>
         </is>
       </c>
-      <c r="M1" s="16" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>prerequisites</t>
         </is>
       </c>
-      <c r="N1" s="16" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="O1" s="16" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" s="16" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="Q1" s="16" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>flags</t>
         </is>
       </c>
-      <c r="R1" s="16" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>meeting</t>
         </is>
       </c>
-      <c r="S1" s="16" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="T1" s="16" t="inlineStr">
+      <c r="T1" s="15" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
       </c>
-      <c r="U1" s="16" t="inlineStr">
+      <c r="U1" s="15" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="V1" s="16" t="inlineStr">
+      <c r="V1" s="15" t="inlineStr">
         <is>
           <t>created</t>
         </is>
       </c>
-      <c r="W1" s="16" t="inlineStr">
+      <c r="W1" s="15" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="X1" s="16" t="inlineStr">
+      <c r="X1" s="15" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>Write down the ideas after the walk</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr"/>
+      <c r="K2" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="L2" s="16" t="inlineStr"/>
+      <c r="M2" s="16" t="inlineStr"/>
+      <c r="N2" s="16" t="inlineStr"/>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="inlineStr">
+        <is>
+          <t>line itself: personal walk brainstorm task</t>
+        </is>
+      </c>
+      <c r="Q2" s="16" t="inlineStr">
+        <is>
+          <t>basis unresolved</t>
+        </is>
+      </c>
+      <c r="R2" s="16" t="inlineStr">
+        <is>
+          <t>Personal note 2026-09-18</t>
+        </is>
+      </c>
+      <c r="S2" s="17" t="inlineStr">
+        <is>
+          <t>unplanned</t>
+        </is>
+      </c>
+      <c r="T2" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="U2" s="18" t="n"/>
+      <c r="V2" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="W2" s="16" t="inlineStr">
+        <is>
+          <t>note-2026-09-18-walk-brainstorm.md</t>
+        </is>
+      </c>
+      <c r="X2" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-18-unassigned-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E2" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="17" t="inlineStr"/>
-      <c r="J2" s="17" t="inlineStr"/>
-      <c r="K2" s="18" t="inlineStr"/>
-      <c r="L2" s="17" t="inlineStr"/>
-      <c r="M2" s="17" t="inlineStr"/>
-      <c r="N2" s="17" t="inlineStr"/>
-      <c r="O2" s="17" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="16" t="inlineStr"/>
+      <c r="J3" s="16" t="inlineStr"/>
+      <c r="K3" s="17" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr"/>
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
-      <c r="P2" s="17" t="inlineStr"/>
-      <c r="Q2" s="17" t="inlineStr"/>
-      <c r="R2" s="17" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr"/>
+      <c r="Q3" s="16" t="inlineStr"/>
+      <c r="R3" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="S3" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T2" s="19" t="n">
+      <c r="T3" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U2" s="19" t="n">
+      <c r="U3" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V2" s="19" t="n">
+      <c r="V3" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W2" s="17" t="inlineStr">
+      <c r="W3" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X2" s="17" t="inlineStr">
+      <c r="X3" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="17" t="inlineStr"/>
-      <c r="J3" s="17" t="inlineStr"/>
-      <c r="K3" s="18" t="inlineStr"/>
-      <c r="L3" s="17" t="inlineStr"/>
-      <c r="M3" s="17" t="inlineStr"/>
-      <c r="N3" s="17" t="inlineStr"/>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="16" t="inlineStr"/>
+      <c r="J4" s="16" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="16" t="inlineStr"/>
+      <c r="M4" s="16" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr"/>
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr"/>
-      <c r="Q3" s="17" t="inlineStr"/>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="P4" s="16" t="inlineStr"/>
+      <c r="Q4" s="16" t="inlineStr"/>
+      <c r="R4" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S3" s="18" t="inlineStr">
+      <c r="S4" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T3" s="19" t="n">
+      <c r="T4" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U3" s="19" t="n">
+      <c r="U4" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V3" s="19" t="n">
+      <c r="V4" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W3" s="17" t="inlineStr">
+      <c r="W4" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X3" s="17" t="inlineStr">
+      <c r="X4" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="17" t="inlineStr"/>
-      <c r="J4" s="17" t="inlineStr"/>
-      <c r="K4" s="18" t="inlineStr"/>
-      <c r="L4" s="17" t="inlineStr"/>
-      <c r="M4" s="17" t="inlineStr"/>
-      <c r="N4" s="17" t="inlineStr"/>
-      <c r="O4" s="17" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="16" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr"/>
+      <c r="N5" s="16" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr">
         <is>
           <t>Change the UI. I'll change it.</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr"/>
-      <c r="Q4" s="17" t="inlineStr"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr"/>
+      <c r="R5" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S4" s="18" t="inlineStr">
+      <c r="S5" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T4" s="19" t="n">
+      <c r="T5" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U4" s="19" t="n">
+      <c r="U5" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V4" s="19" t="n">
+      <c r="V5" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W4" s="17" t="inlineStr">
+      <c r="W5" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X4" s="17" t="inlineStr">
+      <c r="X5" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E6" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr"/>
-      <c r="I5" s="17" t="inlineStr"/>
-      <c r="J5" s="17" t="inlineStr"/>
-      <c r="K5" s="18" t="inlineStr"/>
-      <c r="L5" s="17" t="inlineStr"/>
-      <c r="M5" s="17" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr"/>
-      <c r="O5" s="17" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr"/>
+      <c r="I6" s="16" t="inlineStr"/>
+      <c r="J6" s="16" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr"/>
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr"/>
-      <c r="Q5" s="17" t="inlineStr"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr"/>
+      <c r="Q6" s="16" t="inlineStr"/>
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S5" s="18" t="inlineStr">
+      <c r="S6" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T5" s="19" t="n">
+      <c r="T6" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U5" s="19" t="n">
+      <c r="U6" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V5" s="19" t="n">
+      <c r="V6" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W5" s="17" t="inlineStr">
+      <c r="W6" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X5" s="17" t="inlineStr">
+      <c r="X6" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr"/>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr"/>
+      <c r="I7" s="16" t="inlineStr"/>
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr"/>
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t>user stories you figure out and you show me</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr"/>
-      <c r="Q6" s="17" t="inlineStr"/>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="R7" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S6" s="18" t="inlineStr">
+      <c r="S7" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T6" s="19" t="n">
+      <c r="T7" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U6" s="19" t="n">
+      <c r="U7" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V6" s="19" t="n">
+      <c r="V7" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W6" s="17" t="inlineStr">
+      <c r="W7" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X6" s="17" t="inlineStr">
+      <c r="X7" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="17" t="inlineStr"/>
-      <c r="K7" s="18" t="inlineStr"/>
-      <c r="L7" s="17" t="inlineStr"/>
-      <c r="M7" s="17" t="inlineStr"/>
-      <c r="N7" s="17" t="inlineStr"/>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="16" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr"/>
+      <c r="O8" s="16" t="inlineStr">
         <is>
           <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr"/>
-      <c r="Q7" s="17" t="inlineStr"/>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr"/>
+      <c r="Q8" s="16" t="inlineStr"/>
+      <c r="R8" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S7" s="18" t="inlineStr">
+      <c r="S8" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T7" s="19" t="n">
+      <c r="T8" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U7" s="19" t="n">
+      <c r="U8" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V7" s="19" t="n">
+      <c r="V8" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="W7" s="17" t="inlineStr">
+      <c r="W8" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X7" s="17" t="inlineStr">
+      <c r="X8" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="17" t="inlineStr"/>
-      <c r="J8" s="17" t="inlineStr"/>
-      <c r="K8" s="18" t="inlineStr"/>
-      <c r="L8" s="17" t="inlineStr"/>
-      <c r="M8" s="17" t="inlineStr"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr"/>
+      <c r="I9" s="16" t="inlineStr"/>
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr"/>
-      <c r="Q8" s="17" t="inlineStr"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr"/>
+      <c r="Q9" s="16" t="inlineStr"/>
+      <c r="R9" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S8" s="18" t="inlineStr">
+      <c r="S9" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T8" s="19" t="n">
+      <c r="T9" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U8" s="19" t="n">
+      <c r="U9" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V8" s="19" t="n">
+      <c r="V9" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="W8" s="17" t="inlineStr">
+      <c r="W9" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X8" s="17" t="inlineStr">
+      <c r="X9" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr"/>
-      <c r="I9" s="17" t="inlineStr"/>
-      <c r="J9" s="17" t="inlineStr"/>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="17" t="inlineStr"/>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr"/>
+      <c r="I10" s="16" t="inlineStr"/>
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr"/>
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr"/>
-      <c r="Q9" s="17" t="inlineStr"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="P10" s="16" t="inlineStr"/>
+      <c r="Q10" s="16" t="inlineStr"/>
+      <c r="R10" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S9" s="18" t="inlineStr">
+      <c r="S10" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T9" s="19" t="n">
+      <c r="T10" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U9" s="19" t="n">
+      <c r="U10" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V9" s="19" t="n">
+      <c r="V10" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W9" s="17" t="inlineStr">
+      <c r="W10" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X9" s="17" t="inlineStr">
+      <c r="X10" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="17" t="inlineStr"/>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="K10" s="18" t="inlineStr"/>
-      <c r="L10" s="17" t="inlineStr"/>
-      <c r="M10" s="17" t="inlineStr"/>
-      <c r="N10" s="17" t="inlineStr"/>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr"/>
+      <c r="I11" s="16" t="inlineStr"/>
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr"/>
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr"/>
-      <c r="Q10" s="17" t="inlineStr"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr"/>
+      <c r="R11" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S10" s="18" t="inlineStr">
+      <c r="S11" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T10" s="19" t="n">
+      <c r="T11" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U10" s="19" t="n">
+      <c r="U11" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V10" s="19" t="n">
+      <c r="V11" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W10" s="17" t="inlineStr">
+      <c r="W11" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X10" s="17" t="inlineStr">
+      <c r="X11" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E12" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr"/>
-      <c r="I11" s="17" t="inlineStr"/>
-      <c r="J11" s="17" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
-      <c r="L11" s="17" t="inlineStr"/>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr"/>
+      <c r="I12" s="16" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr"/>
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr"/>
-      <c r="Q11" s="17" t="inlineStr"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="P12" s="16" t="inlineStr"/>
+      <c r="Q12" s="16" t="inlineStr"/>
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S11" s="18" t="inlineStr">
+      <c r="S12" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T11" s="19" t="n">
+      <c r="T12" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U11" s="19" t="n">
+      <c r="U12" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V11" s="19" t="n">
+      <c r="V12" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W11" s="17" t="inlineStr">
+      <c r="W12" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X11" s="17" t="inlineStr">
+      <c r="X12" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E13" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="17" t="inlineStr"/>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="18" t="inlineStr"/>
-      <c r="L12" s="17" t="inlineStr"/>
-      <c r="M12" s="17" t="inlineStr"/>
-      <c r="N12" s="17" t="inlineStr"/>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr"/>
+      <c r="I13" s="16" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr"/>
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr"/>
-      <c r="Q12" s="17" t="inlineStr"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="R13" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S12" s="18" t="inlineStr">
+      <c r="S13" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T12" s="19" t="n">
+      <c r="T13" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U12" s="19" t="n">
+      <c r="U13" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V12" s="19" t="n">
+      <c r="V13" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W12" s="17" t="inlineStr">
+      <c r="W13" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X12" s="17" t="inlineStr">
+      <c r="X13" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr"/>
-      <c r="I13" s="17" t="inlineStr"/>
-      <c r="J13" s="17" t="inlineStr"/>
-      <c r="K13" s="18" t="inlineStr"/>
-      <c r="L13" s="17" t="inlineStr"/>
-      <c r="M13" s="17" t="inlineStr"/>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr"/>
+      <c r="I14" s="16" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr"/>
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr"/>
-      <c r="Q13" s="17" t="inlineStr"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="P14" s="16" t="inlineStr"/>
+      <c r="Q14" s="16" t="inlineStr"/>
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S13" s="18" t="inlineStr">
+      <c r="S14" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T13" s="19" t="n">
+      <c r="T14" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U13" s="19" t="n">
+      <c r="U14" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V13" s="19" t="n">
+      <c r="V14" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W13" s="17" t="inlineStr">
+      <c r="W14" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X13" s="17" t="inlineStr">
+      <c r="X14" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr"/>
-      <c r="I14" s="17" t="inlineStr"/>
-      <c r="J14" s="17" t="inlineStr"/>
-      <c r="K14" s="18" t="inlineStr"/>
-      <c r="L14" s="17" t="inlineStr"/>
-      <c r="M14" s="17" t="inlineStr"/>
-      <c r="N14" s="17" t="inlineStr"/>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr"/>
+      <c r="I15" s="16" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr"/>
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr"/>
-      <c r="Q14" s="17" t="inlineStr"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr"/>
+      <c r="R15" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S14" s="18" t="inlineStr">
+      <c r="S15" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T14" s="19" t="n">
+      <c r="T15" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U14" s="19" t="n">
+      <c r="U15" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V14" s="19" t="n">
+      <c r="V15" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W14" s="17" t="inlineStr">
+      <c r="W15" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X14" s="17" t="inlineStr">
+      <c r="X15" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Ashwini</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="17" t="inlineStr"/>
-      <c r="J15" s="17" t="inlineStr"/>
-      <c r="K15" s="18" t="inlineStr"/>
-      <c r="L15" s="17" t="inlineStr"/>
-      <c r="M15" s="17" t="inlineStr"/>
-      <c r="N15" s="17" t="inlineStr"/>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr"/>
+      <c r="I16" s="16" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr"/>
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr"/>
-      <c r="Q15" s="17" t="inlineStr"/>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="P16" s="16" t="inlineStr"/>
+      <c r="Q16" s="16" t="inlineStr"/>
+      <c r="R16" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S15" s="18" t="inlineStr">
+      <c r="S16" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T15" s="19" t="n">
+      <c r="T16" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U15" s="19" t="n">
+      <c r="U16" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V15" s="19" t="n">
+      <c r="V16" s="18" t="n">
         <v>46280</v>
       </c>
-      <c r="W15" s="17" t="inlineStr">
+      <c r="W16" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X15" s="17" t="inlineStr">
+      <c r="X16" s="16" t="inlineStr">
         <is>
           <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr"/>
-      <c r="K16" s="18" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>half-day</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr"/>
-      <c r="M16" s="17" t="inlineStr">
+      <c r="L17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr">
         <is>
           <t>List of new columns/tables from this CR</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr"/>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="N17" s="16" t="inlineStr"/>
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
         </is>
       </c>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="P17" s="16" t="inlineStr">
         <is>
           <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr"/>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="Q17" s="16" t="inlineStr"/>
+      <c r="R17" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="S16" s="18" t="inlineStr">
+      <c r="S17" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T16" s="19" t="n">
+      <c r="T17" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="U16" s="19" t="n">
+      <c r="U17" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="V16" s="19" t="n">
+      <c r="V17" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W16" s="17" t="inlineStr">
+      <c r="W17" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="X16" s="17" t="inlineStr">
+      <c r="X17" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-01</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr"/>
-      <c r="I17" s="17" t="inlineStr"/>
-      <c r="J17" s="17" t="inlineStr"/>
-      <c r="K17" s="18" t="inlineStr"/>
-      <c r="L17" s="17" t="inlineStr"/>
-      <c r="M17" s="17" t="inlineStr"/>
-      <c r="N17" s="17" t="inlineStr"/>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr"/>
+      <c r="I18" s="16" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr"/>
+      <c r="O18" s="16" t="inlineStr">
         <is>
           <t>I will speak to Lakshmi, plan development plan with model that's it</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr"/>
-      <c r="Q17" s="17" t="inlineStr"/>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="P18" s="16" t="inlineStr"/>
+      <c r="Q18" s="16" t="inlineStr"/>
+      <c r="R18" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S17" s="18" t="inlineStr">
+      <c r="S18" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T17" s="19" t="n">
+      <c r="T18" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U17" s="19" t="n">
+      <c r="U18" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V17" s="19" t="n">
+      <c r="V18" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W17" s="17" t="inlineStr">
+      <c r="W18" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X17" s="17" t="inlineStr">
+      <c r="X18" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Johan</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr"/>
-      <c r="I18" s="17" t="inlineStr"/>
-      <c r="J18" s="17" t="inlineStr"/>
-      <c r="K18" s="18" t="inlineStr"/>
-      <c r="L18" s="17" t="inlineStr"/>
-      <c r="M18" s="17" t="inlineStr"/>
-      <c r="N18" s="17" t="inlineStr"/>
-      <c r="O18" s="17" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr"/>
-      <c r="Q18" s="17" t="inlineStr"/>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="P19" s="16" t="inlineStr"/>
+      <c r="Q19" s="16" t="inlineStr"/>
+      <c r="R19" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S18" s="18" t="inlineStr">
+      <c r="S19" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T18" s="19" t="n">
+      <c r="T19" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U18" s="19" t="n">
+      <c r="U19" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V18" s="19" t="n">
+      <c r="V19" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W18" s="17" t="inlineStr">
+      <c r="W19" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X18" s="17" t="inlineStr">
+      <c r="X19" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E20" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr"/>
-      <c r="I19" s="17" t="inlineStr"/>
-      <c r="J19" s="17" t="inlineStr"/>
-      <c r="K19" s="18" t="inlineStr"/>
-      <c r="L19" s="17" t="inlineStr"/>
-      <c r="M19" s="17" t="inlineStr"/>
-      <c r="N19" s="17" t="inlineStr"/>
-      <c r="O19" s="17" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="16" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr"/>
+      <c r="O20" s="16" t="inlineStr">
         <is>
           <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
-      <c r="P19" s="17" t="inlineStr"/>
-      <c r="Q19" s="17" t="inlineStr"/>
-      <c r="R19" s="17" t="inlineStr">
+      <c r="P20" s="16" t="inlineStr"/>
+      <c r="Q20" s="16" t="inlineStr"/>
+      <c r="R20" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S19" s="18" t="inlineStr">
+      <c r="S20" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T19" s="19" t="n">
+      <c r="T20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U19" s="19" t="n">
+      <c r="U20" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V19" s="19" t="n">
+      <c r="V20" s="18" t="n">
         <v>46276</v>
       </c>
-      <c r="W19" s="17" t="inlineStr">
+      <c r="W20" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X19" s="17" t="inlineStr">
+      <c r="X20" s="16" t="inlineStr">
         <is>
           <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Samuel</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E21" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr"/>
-      <c r="I20" s="17" t="inlineStr"/>
-      <c r="J20" s="17" t="inlineStr"/>
-      <c r="K20" s="18" t="inlineStr"/>
-      <c r="L20" s="17" t="inlineStr"/>
-      <c r="M20" s="17" t="inlineStr"/>
-      <c r="N20" s="17" t="inlineStr"/>
-      <c r="O20" s="17" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr"/>
+      <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr"/>
+      <c r="N21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="inlineStr">
         <is>
           <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr"/>
-      <c r="Q20" s="17" t="inlineStr"/>
-      <c r="R20" s="17" t="inlineStr">
+      <c r="P21" s="16" t="inlineStr"/>
+      <c r="Q21" s="16" t="inlineStr"/>
+      <c r="R21" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
-      <c r="S20" s="18" t="inlineStr">
+      <c r="S21" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T20" s="19" t="n">
+      <c r="T21" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="U20" s="19" t="n">
+      <c r="U21" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="V20" s="19" t="n">
+      <c r="V21" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W20" s="17" t="inlineStr">
+      <c r="W21" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
-      <c r="X20" s="17" t="inlineStr">
+      <c r="X21" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Sarathchandra Babu</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E22" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>coordinate</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>Send the poll to the team and collect responses.</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr"/>
-      <c r="K21" s="18" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="L21" s="17" t="inlineStr"/>
-      <c r="M21" s="17" t="inlineStr"/>
-      <c r="N21" s="17" t="inlineStr"/>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr"/>
+      <c r="O22" s="16" t="inlineStr">
         <is>
           <t>Or, if you can put a poll in one of these, let's see here.</t>
         </is>
       </c>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="P22" s="16" t="inlineStr">
         <is>
           <t>D-2026-09-17-02</t>
         </is>
       </c>
-      <c r="Q21" s="17" t="inlineStr"/>
-      <c r="R21" s="17" t="inlineStr">
+      <c r="Q22" s="16" t="inlineStr"/>
+      <c r="R22" s="16" t="inlineStr">
         <is>
           <t>Code Apps Learning Curriculum Structure Discussion</t>
         </is>
       </c>
-      <c r="S21" s="18" t="inlineStr">
+      <c r="S22" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T21" s="19" t="n">
+      <c r="T22" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="U21" s="19" t="n">
+      <c r="U22" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="V21" s="19" t="n">
+      <c r="V22" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="W21" s="17" t="inlineStr">
+      <c r="W22" s="16" t="inlineStr">
         <is>
           <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
         </is>
       </c>
-      <c r="X21" s="17" t="inlineStr">
+      <c r="X22" s="16" t="inlineStr">
         <is>
           <t>2026-09-17-unassigned-01</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Adwaith</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr"/>
-      <c r="K22" s="18" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr"/>
-      <c r="M22" s="17" t="inlineStr"/>
-      <c r="N22" s="17" t="inlineStr"/>
-      <c r="O22" s="17" t="inlineStr">
+      <c r="L23" s="16" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr"/>
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
         </is>
       </c>
-      <c r="P22" s="17" t="inlineStr">
+      <c r="P23" s="16" t="inlineStr">
         <is>
           <t>CR section 7.4 Notifications</t>
         </is>
       </c>
-      <c r="Q22" s="17" t="inlineStr"/>
-      <c r="R22" s="17" t="inlineStr">
+      <c r="Q23" s="16" t="inlineStr"/>
+      <c r="R23" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="S22" s="18" t="inlineStr">
+      <c r="S23" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T22" s="19" t="n">
+      <c r="T23" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="U22" s="19" t="n">
+      <c r="U23" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="V22" s="19" t="n">
+      <c r="V23" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W22" s="17" t="inlineStr">
+      <c r="W23" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="X22" s="17" t="inlineStr">
+      <c r="X23" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-02</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Ayush</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>lsp</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>decide</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr"/>
-      <c r="K23" s="18" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr"/>
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L23" s="17" t="inlineStr"/>
-      <c r="M23" s="17" t="inlineStr"/>
-      <c r="N23" s="17" t="inlineStr"/>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="L24" s="16" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr"/>
+      <c r="O24" s="16" t="inlineStr">
         <is>
           <t>Agree a retention or archival policy for closed periodic closures.</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P24" s="16" t="inlineStr">
         <is>
           <t>CR section 8.6 Sizing</t>
         </is>
       </c>
-      <c r="Q23" s="17" t="inlineStr"/>
-      <c r="R23" s="17" t="inlineStr">
+      <c r="Q24" s="16" t="inlineStr"/>
+      <c r="R24" s="16" t="inlineStr">
         <is>
           <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
-      <c r="S23" s="18" t="inlineStr">
+      <c r="S24" s="17" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="T23" s="19" t="n">
+      <c r="T24" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="U23" s="19" t="n">
+      <c r="U24" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="V23" s="19" t="n">
+      <c r="V24" s="18" t="n">
         <v>46281</v>
       </c>
-      <c r="W23" s="17" t="inlineStr">
+      <c r="W24" s="16" t="inlineStr">
         <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="X23" s="17" t="inlineStr">
+      <c r="X24" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -443,12 +443,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10</f>
+              <f>'Dashboard'!$B$10:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$10</f>
+              <f>'Dashboard'!$C$10:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -473,12 +473,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10</f>
+              <f>'Dashboard'!$B$10:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$10</f>
+              <f>'Dashboard'!$D$10:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10</f>
+              <f>'Dashboard'!$B$10:$B$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$10</f>
+              <f>'Dashboard'!$E$10:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -683,8 +683,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X24" headerRowCount="1">
-  <autoFilter ref="A1:X24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X27" headerRowCount="1">
+  <autoFilter ref="A1:X27"/>
   <tableColumns count="24">
     <tableColumn id="1" name="task"/>
     <tableColumn id="2" name="owner"/>
@@ -1036,7 +1036,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-18). Edits that should stick belong in the Google Sheet.</t>
+          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-21). Edits that should stick belong in the Google Sheet.</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C10" s="11">
@@ -1179,29 +1179,83 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Ashwini</t>
+        </is>
+      </c>
+      <c r="C11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B11,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C11" s="14">
-        <f>SUM(C10:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="14">
-        <f>SUM(D10:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="14">
-        <f>SUM(E10:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="14">
-        <f>SUM(F10:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="14">
-        <f>SUM(G10:G10)</f>
+      <c r="C13" s="14">
+        <f>SUM(C10:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="14">
+        <f>SUM(D10:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="14">
+        <f>SUM(E10:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="14">
+        <f>SUM(F10:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="14">
+        <f>SUM(G10:G12)</f>
         <v/>
       </c>
     </row>
@@ -1533,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1687,17 +1741,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+          <t>Verify and add date-based validation for inserting a new stage above or between existing stages in the plan tree.</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
@@ -1706,32 +1760,32 @@
         </is>
       </c>
       <c r="E2" s="18" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G2" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>Intelligent Tracker</t>
         </is>
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>review</t>
         </is>
       </c>
       <c r="I2" s="16" t="inlineStr">
         <is>
-          <t>Write down the ideas after the walk</t>
+          <t>Add validation that checks a newly inserted stage's dates against neighboring stages' start/close dates.</t>
         </is>
       </c>
       <c r="J2" s="16" t="inlineStr"/>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L2" s="16" t="inlineStr"/>
@@ -1739,70 +1793,66 @@
       <c r="N2" s="16" t="inlineStr"/>
       <c r="O2" s="16" t="inlineStr">
         <is>
-          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
+          <t>So, just okay, so we check that.</t>
         </is>
       </c>
       <c r="P2" s="16" t="inlineStr">
         <is>
-          <t>line itself: personal walk brainstorm task</t>
-        </is>
-      </c>
-      <c r="Q2" s="16" t="inlineStr">
-        <is>
-          <t>basis unresolved</t>
-        </is>
-      </c>
+          <t>based on the dates, you have to get validation, cant be based on this date or the close date over here</t>
+        </is>
+      </c>
+      <c r="Q2" s="16" t="inlineStr"/>
       <c r="R2" s="16" t="inlineStr">
         <is>
-          <t>Personal note 2026-09-18</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S2" s="17" t="inlineStr">
         <is>
-          <t>unplanned</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="T2" s="18" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="U2" s="18" t="n"/>
       <c r="V2" s="18" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="W2" s="16" t="inlineStr">
         <is>
-          <t>note-2026-09-18-walk-brainstorm.md</t>
+          <t>2026-09-21-activity-tracker-sync.docx</t>
         </is>
       </c>
       <c r="X2" s="16" t="inlineStr">
         <is>
-          <t>2026-09-18-unassigned-01</t>
+          <t>2026-09-21-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Sign off on the reviewed database design after today's walkthrough.</t>
+          <t>Add a 'my tasks' filter to the plan tree so team members can see only the tasks assigned to them.</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E3" s="18" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
@@ -1814,19 +1864,35 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Implement a my-tasks filter option on the plan tree screen.</t>
+        </is>
+      </c>
       <c r="J3" s="16" t="inlineStr"/>
-      <c r="K3" s="17" t="inlineStr"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L3" s="16" t="inlineStr"/>
       <c r="M3" s="16" t="inlineStr"/>
       <c r="N3" s="16" t="inlineStr"/>
       <c r="O3" s="16" t="inlineStr">
         <is>
-          <t>I will be signing off on the Debi after the review</t>
-        </is>
-      </c>
-      <c r="P3" s="16" t="inlineStr"/>
+          <t>Yes, yes, sir, we can give filters.</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>So my task or something like that, if you can give, that makes easy, you know, life easy for them.</t>
+        </is>
+      </c>
       <c r="Q3" s="16" t="inlineStr"/>
       <c r="R3" s="16" t="inlineStr">
         <is>
@@ -1839,48 +1905,46 @@
         </is>
       </c>
       <c r="T3" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U3" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46286</v>
+      </c>
+      <c r="U3" s="18" t="n"/>
       <c r="V3" s="18" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="W3" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-21-activity-tracker-sync.docx</t>
         </is>
       </c>
       <c r="X3" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-01</t>
+          <t>2026-09-21-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Work with Ashwini on the overall workflow solution design document.</t>
+          <t>Set and add the first demo date to the project plan.</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E4" s="18" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
@@ -1892,19 +1956,35 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr"/>
-      <c r="I4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Add the planned first-demo date to the project plan schedule.</t>
+        </is>
+      </c>
       <c r="J4" s="16" t="inlineStr"/>
-      <c r="K4" s="17" t="inlineStr"/>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
       <c r="L4" s="16" t="inlineStr"/>
       <c r="M4" s="16" t="inlineStr"/>
       <c r="N4" s="16" t="inlineStr"/>
       <c r="O4" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi and I will be working on the proper workflow solution design</t>
-        </is>
-      </c>
-      <c r="P4" s="16" t="inlineStr"/>
+          <t>No, please put the date where we can have the first demo.</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>No, please put the date where we can have the first demo.</t>
+        </is>
+      </c>
       <c r="Q4" s="16" t="inlineStr"/>
       <c r="R4" s="16" t="inlineStr">
         <is>
@@ -1917,112 +1997,128 @@
         </is>
       </c>
       <c r="T4" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U4" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46286</v>
+      </c>
+      <c r="U4" s="18" t="n"/>
       <c r="V4" s="18" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="W4" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-21-activity-tracker-sync.docx</t>
         </is>
       </c>
       <c r="X4" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-04</t>
+          <t>2026-09-21-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
+          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr"/>
-      <c r="I5" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Write down the ideas after the walk</t>
+        </is>
+      </c>
       <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
       <c r="L5" s="16" t="inlineStr"/>
       <c r="M5" s="16" t="inlineStr"/>
       <c r="N5" s="16" t="inlineStr"/>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>Change the UI. I'll change it.</t>
-        </is>
-      </c>
-      <c r="P5" s="16" t="inlineStr"/>
-      <c r="Q5" s="16" t="inlineStr"/>
+          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>line itself: personal walk brainstorm task</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>basis unresolved</t>
+        </is>
+      </c>
       <c r="R5" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Personal note 2026-09-18</t>
         </is>
       </c>
       <c r="S5" s="17" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>unplanned</t>
         </is>
       </c>
       <c r="T5" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U5" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46283</v>
+      </c>
+      <c r="U5" s="18" t="n"/>
       <c r="V5" s="18" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="W5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>note-2026-09-18-walk-brainstorm.md</t>
         </is>
       </c>
       <c r="X5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-05</t>
+          <t>2026-09-18-unassigned-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
+          <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -2057,7 +2153,7 @@
       <c r="N6" s="16" t="inlineStr"/>
       <c r="O6" s="16" t="inlineStr">
         <is>
-          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
+          <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
       <c r="P6" s="16" t="inlineStr"/>
@@ -2088,19 +2184,19 @@
       </c>
       <c r="X6" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-06</t>
+          <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
+          <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2135,7 +2231,7 @@
       <c r="N7" s="16" t="inlineStr"/>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>user stories you figure out and you show me</t>
+          <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr"/>
@@ -2166,19 +2262,19 @@
       </c>
       <c r="X7" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-07</t>
+          <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
+          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -2192,7 +2288,7 @@
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -2213,7 +2309,7 @@
       <c r="N8" s="16" t="inlineStr"/>
       <c r="O8" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
+          <t>Change the UI. I'll change it.</t>
         </is>
       </c>
       <c r="P8" s="16" t="inlineStr"/>
@@ -2235,28 +2331,28 @@
         <v>46282</v>
       </c>
       <c r="V8" s="18" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="W8" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X8" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-01</t>
+          <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
+          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -2270,7 +2366,7 @@
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -2288,14 +2384,10 @@
       <c r="K9" s="17" t="inlineStr"/>
       <c r="L9" s="16" t="inlineStr"/>
       <c r="M9" s="16" t="inlineStr"/>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
-        </is>
-      </c>
+      <c r="N9" s="16" t="inlineStr"/>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
+          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr"/>
@@ -2311,34 +2403,34 @@
         </is>
       </c>
       <c r="T9" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U9" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V9" s="18" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="W9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-02</t>
+          <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
+          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2352,7 +2444,7 @@
         </is>
       </c>
       <c r="E10" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -2373,7 +2465,7 @@
       <c r="N10" s="16" t="inlineStr"/>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
+          <t>user stories you figure out and you show me</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr"/>
@@ -2389,29 +2481,29 @@
         </is>
       </c>
       <c r="T10" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U10" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V10" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-03</t>
+          <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
+          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -2430,7 +2522,7 @@
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -2451,7 +2543,7 @@
       <c r="N11" s="16" t="inlineStr"/>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
+          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr"/>
@@ -2467,34 +2559,34 @@
         </is>
       </c>
       <c r="T11" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V11" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="W11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-04</t>
+          <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
+          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2526,10 +2618,14 @@
       <c r="K12" s="17" t="inlineStr"/>
       <c r="L12" s="16" t="inlineStr"/>
       <c r="M12" s="16" t="inlineStr"/>
-      <c r="N12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
+        </is>
+      </c>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
+          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
       <c r="P12" s="16" t="inlineStr"/>
@@ -2551,28 +2647,28 @@
         <v>46283</v>
       </c>
       <c r="V12" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="W12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-05</t>
+          <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
+          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -2607,7 +2703,7 @@
       <c r="N13" s="16" t="inlineStr"/>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr"/>
@@ -2638,19 +2734,19 @@
       </c>
       <c r="X13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-07</t>
+          <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
+          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -2685,7 +2781,7 @@
       <c r="N14" s="16" t="inlineStr"/>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr"/>
@@ -2701,10 +2797,10 @@
         </is>
       </c>
       <c r="T14" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V14" s="18" t="n">
         <v>46281</v>
@@ -2716,19 +2812,19 @@
       </c>
       <c r="X14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
+          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -2763,7 +2859,7 @@
       <c r="N15" s="16" t="inlineStr"/>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
+          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr"/>
@@ -2779,10 +2875,10 @@
         </is>
       </c>
       <c r="T15" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V15" s="18" t="n">
         <v>46281</v>
@@ -2794,19 +2890,19 @@
       </c>
       <c r="X15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-06</t>
+          <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
+          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -2819,7 +2915,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n"/>
+      <c r="E16" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -2839,7 +2937,7 @@
       <c r="N16" s="16" t="inlineStr"/>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>Yeah, that we will show you on the website.</t>
+          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr"/>
@@ -2861,28 +2959,28 @@
         <v>46283</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="W16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -2895,54 +2993,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E17" s="18" t="n"/>
+      <c r="E17" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr"/>
       <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>half-day</t>
-        </is>
-      </c>
+      <c r="K17" s="17" t="inlineStr"/>
       <c r="L17" s="16" t="inlineStr"/>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
+      <c r="M17" s="16" t="inlineStr"/>
       <c r="N17" s="16" t="inlineStr"/>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
-        </is>
-      </c>
-      <c r="P17" s="16" t="inlineStr">
-        <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
-        </is>
-      </c>
+          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+        </is>
+      </c>
+      <c r="P17" s="16" t="inlineStr"/>
       <c r="Q17" s="16" t="inlineStr"/>
       <c r="R17" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S17" s="17" t="inlineStr">
@@ -2951,39 +3031,39 @@
         </is>
       </c>
       <c r="T17" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="V17" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="W17" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X17" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-01</t>
+          <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -2992,7 +3072,7 @@
         </is>
       </c>
       <c r="E18" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -3013,7 +3093,7 @@
       <c r="N18" s="16" t="inlineStr"/>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
@@ -3029,39 +3109,39 @@
         </is>
       </c>
       <c r="T18" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U18" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V18" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
+          <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -3069,9 +3149,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E19" s="18" t="n">
-        <v>46276</v>
-      </c>
+      <c r="E19" s="18" t="n"/>
       <c r="F19" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -3091,7 +3169,7 @@
       <c r="N19" s="16" t="inlineStr"/>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr"/>
@@ -3107,39 +3185,39 @@
         </is>
       </c>
       <c r="T19" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
+          <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -3147,36 +3225,54 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E20" s="18" t="n">
-        <v>46276</v>
-      </c>
+      <c r="E20" s="18" t="n"/>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>lsp</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr"/>
-      <c r="I20" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
       <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="17" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
       <c r="L20" s="16" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
       <c r="N20" s="16" t="inlineStr"/>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr"/>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
       <c r="Q20" s="16" t="inlineStr"/>
       <c r="R20" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
       <c r="S20" s="17" t="inlineStr">
@@ -3185,34 +3281,34 @@
         </is>
       </c>
       <c r="T20" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="U20" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
       <c r="X20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-16-lsp-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3226,7 +3322,7 @@
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -3247,7 +3343,7 @@
       <c r="N21" s="16" t="inlineStr"/>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr"/>
@@ -3269,28 +3365,28 @@
         <v>46283</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-01</t>
+          <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Sarathchandra Babu</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -3304,51 +3400,35 @@
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>coordinate</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>Send the poll to the team and collect responses.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr"/>
+      <c r="I22" s="16" t="inlineStr"/>
       <c r="J22" s="16" t="inlineStr"/>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K22" s="17" t="inlineStr"/>
       <c r="L22" s="16" t="inlineStr"/>
       <c r="M22" s="16" t="inlineStr"/>
       <c r="N22" s="16" t="inlineStr"/>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>Or, if you can put a poll in one of these, let's see here.</t>
-        </is>
-      </c>
-      <c r="P22" s="16" t="inlineStr">
-        <is>
-          <t>D-2026-09-17-02</t>
-        </is>
-      </c>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P22" s="16" t="inlineStr"/>
       <c r="Q22" s="16" t="inlineStr"/>
       <c r="R22" s="16" t="inlineStr">
         <is>
-          <t>Code Apps Learning Curriculum Structure Discussion</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S22" s="17" t="inlineStr">
@@ -3363,28 +3443,28 @@
         <v>46282</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="W22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-unassigned-01</t>
+          <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Adwaith</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -3397,50 +3477,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E23" s="18" t="n"/>
+      <c r="E23" s="18" t="n">
+        <v>46276</v>
+      </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr"/>
+      <c r="I23" s="16" t="inlineStr"/>
       <c r="J23" s="16" t="inlineStr"/>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K23" s="17" t="inlineStr"/>
       <c r="L23" s="16" t="inlineStr"/>
       <c r="M23" s="16" t="inlineStr"/>
       <c r="N23" s="16" t="inlineStr"/>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
-        </is>
-      </c>
-      <c r="P23" s="16" t="inlineStr">
-        <is>
-          <t>CR section 7.4 Notifications</t>
-        </is>
-      </c>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P23" s="16" t="inlineStr"/>
       <c r="Q23" s="16" t="inlineStr"/>
       <c r="R23" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S23" s="17" t="inlineStr">
@@ -3449,39 +3515,39 @@
         </is>
       </c>
       <c r="T23" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W23" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-02</t>
+          <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -3489,50 +3555,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E24" s="18" t="n"/>
+      <c r="E24" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>decide</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr"/>
+      <c r="I24" s="16" t="inlineStr"/>
       <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K24" s="17" t="inlineStr"/>
       <c r="L24" s="16" t="inlineStr"/>
       <c r="M24" s="16" t="inlineStr"/>
       <c r="N24" s="16" t="inlineStr"/>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>Agree a retention or archival policy for closed periodic closures.</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr">
-        <is>
-          <t>CR section 8.6 Sizing</t>
-        </is>
-      </c>
+          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr"/>
       <c r="Q24" s="16" t="inlineStr"/>
       <c r="R24" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S24" s="17" t="inlineStr">
@@ -3541,20 +3593,298 @@
         </is>
       </c>
       <c r="T24" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="V24" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="W24" s="16" t="inlineStr">
         <is>
+          <t>2026-09-16-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="X24" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-intelligent-tracker-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Sarathchandra Babu</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>Send the poll to the team and collect responses.</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr"/>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr"/>
+      <c r="N25" s="16" t="inlineStr"/>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>Or, if you can put a poll in one of these, let's see here.</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>D-2026-09-17-02</t>
+        </is>
+      </c>
+      <c r="Q25" s="16" t="inlineStr"/>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t>Code Apps Learning Curriculum Structure Discussion</t>
+        </is>
+      </c>
+      <c r="S25" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T25" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U25" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="V25" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="W25" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+        </is>
+      </c>
+      <c r="X25" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-17-unassigned-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Adwaith</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr"/>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr"/>
+      <c r="N26" s="16" t="inlineStr"/>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
+        </is>
+      </c>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>CR section 7.4 Notifications</t>
+        </is>
+      </c>
+      <c r="Q26" s="16" t="inlineStr"/>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="S26" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T26" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U26" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V26" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W26" s="16" t="inlineStr">
+        <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="X24" s="16" t="inlineStr">
+      <c r="X26" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr"/>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L27" s="16" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr"/>
+      <c r="N27" s="16" t="inlineStr"/>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>Agree a retention or archival policy for closed periodic closures.</t>
+        </is>
+      </c>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t>CR section 8.6 Sizing</t>
+        </is>
+      </c>
+      <c r="Q27" s="16" t="inlineStr"/>
+      <c r="R27" s="16" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="S27" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T27" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U27" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V27" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W27" s="16" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="X27" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -443,12 +443,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$12</f>
+              <f>'Dashboard'!$B$10:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$10:$C$12</f>
+              <f>'Dashboard'!$C$10:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -473,12 +473,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$12</f>
+              <f>'Dashboard'!$B$10:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$10:$D$12</f>
+              <f>'Dashboard'!$D$10:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$12</f>
+              <f>'Dashboard'!$B$10:$B$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$10:$E$12</f>
+              <f>'Dashboard'!$E$10:$E$11</f>
             </numRef>
           </val>
         </ser>
@@ -1206,56 +1206,29 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Ayush</t>
-        </is>
-      </c>
-      <c r="C12" s="11">
-        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P1"))</f>
-        <v/>
-      </c>
-      <c r="D12" s="11">
-        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P2"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="11">
-        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P3"))</f>
-        <v/>
-      </c>
-      <c r="F12" s="12">
-        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
-        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C13" s="14">
-        <f>SUM(C10:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>SUM(D10:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>SUM(E10:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="14">
-        <f>SUM(F10:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>SUM(G10:G12)</f>
+      <c r="C12" s="14">
+        <f>SUM(C10:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="14">
+        <f>SUM(D10:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="14">
+        <f>SUM(E10:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <f>SUM(F10:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="14">
+        <f>SUM(G10:G11)</f>
         <v/>
       </c>
     </row>
@@ -2017,108 +1990,90 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+          <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>Write down the ideas after the walk</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="16" t="inlineStr"/>
       <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K5" s="17" t="inlineStr"/>
       <c r="L5" s="16" t="inlineStr"/>
       <c r="M5" s="16" t="inlineStr"/>
       <c r="N5" s="16" t="inlineStr"/>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
-        </is>
-      </c>
-      <c r="P5" s="16" t="inlineStr">
-        <is>
-          <t>line itself: personal walk brainstorm task</t>
-        </is>
-      </c>
-      <c r="Q5" s="16" t="inlineStr">
-        <is>
-          <t>basis unresolved</t>
-        </is>
-      </c>
+          <t>I will be signing off on the Debi after the review</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr"/>
       <c r="R5" s="16" t="inlineStr">
         <is>
-          <t>Personal note 2026-09-18</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S5" s="17" t="inlineStr">
         <is>
-          <t>unplanned</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="T5" s="18" t="n">
-        <v>46283</v>
-      </c>
-      <c r="U5" s="18" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="U5" s="18" t="n">
+        <v>46282</v>
+      </c>
       <c r="V5" s="18" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="W5" s="16" t="inlineStr">
         <is>
-          <t>note-2026-09-18-walk-brainstorm.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-18-unassigned-01</t>
+          <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Sign off on the reviewed database design after today's walkthrough.</t>
+          <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -2153,7 +2108,7 @@
       <c r="N6" s="16" t="inlineStr"/>
       <c r="O6" s="16" t="inlineStr">
         <is>
-          <t>I will be signing off on the Debi after the review</t>
+          <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
       <c r="P6" s="16" t="inlineStr"/>
@@ -2184,19 +2139,19 @@
       </c>
       <c r="X6" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-01</t>
+          <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Work with Ashwini on the overall workflow solution design document.</t>
+          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2231,7 +2186,7 @@
       <c r="N7" s="16" t="inlineStr"/>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi and I will be working on the proper workflow solution design</t>
+          <t>Change the UI. I'll change it.</t>
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr"/>
@@ -2262,14 +2217,14 @@
       </c>
       <c r="X7" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-04</t>
+          <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
+          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -2309,7 +2264,7 @@
       <c r="N8" s="16" t="inlineStr"/>
       <c r="O8" s="16" t="inlineStr">
         <is>
-          <t>Change the UI. I'll change it.</t>
+          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
       <c r="P8" s="16" t="inlineStr"/>
@@ -2340,19 +2295,19 @@
       </c>
       <c r="X8" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-05</t>
+          <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
+          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -2387,7 +2342,7 @@
       <c r="N9" s="16" t="inlineStr"/>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
+          <t>user stories you figure out and you show me</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr"/>
@@ -2418,19 +2373,19 @@
       </c>
       <c r="X9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-06</t>
+          <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
+          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2444,7 +2399,7 @@
         </is>
       </c>
       <c r="E10" s="18" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -2465,7 +2420,7 @@
       <c r="N10" s="16" t="inlineStr"/>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>user stories you figure out and you show me</t>
+          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr"/>
@@ -2487,28 +2442,28 @@
         <v>46282</v>
       </c>
       <c r="V10" s="18" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="W10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-07</t>
+          <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
+          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2522,7 +2477,7 @@
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -2540,10 +2495,14 @@
       <c r="K11" s="17" t="inlineStr"/>
       <c r="L11" s="16" t="inlineStr"/>
       <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
+        </is>
+      </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
+          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr"/>
@@ -2559,10 +2518,10 @@
         </is>
       </c>
       <c r="T11" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U11" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V11" s="18" t="n">
         <v>46280</v>
@@ -2574,19 +2533,19 @@
       </c>
       <c r="X11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-01</t>
+          <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
+          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2618,14 +2577,10 @@
       <c r="K12" s="17" t="inlineStr"/>
       <c r="L12" s="16" t="inlineStr"/>
       <c r="M12" s="16" t="inlineStr"/>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
-        </is>
-      </c>
+      <c r="N12" s="16" t="inlineStr"/>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
+          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
       <c r="P12" s="16" t="inlineStr"/>
@@ -2647,28 +2602,28 @@
         <v>46283</v>
       </c>
       <c r="V12" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="W12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
+          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -2703,7 +2658,7 @@
       <c r="N13" s="16" t="inlineStr"/>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
+          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr"/>
@@ -2734,14 +2689,14 @@
       </c>
       <c r="X13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
+          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -2781,7 +2736,7 @@
       <c r="N14" s="16" t="inlineStr"/>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
+          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr"/>
@@ -2812,19 +2767,19 @@
       </c>
       <c r="X14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-04</t>
+          <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
+          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -2859,7 +2814,7 @@
       <c r="N15" s="16" t="inlineStr"/>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
+          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr"/>
@@ -2890,19 +2845,19 @@
       </c>
       <c r="X15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-05</t>
+          <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
+          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -2937,7 +2892,7 @@
       <c r="N16" s="16" t="inlineStr"/>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr"/>
@@ -2953,10 +2908,10 @@
         </is>
       </c>
       <c r="T16" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V16" s="18" t="n">
         <v>46281</v>
@@ -2968,14 +2923,14 @@
       </c>
       <c r="X16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-07</t>
+          <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
+          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
@@ -3015,7 +2970,7 @@
       <c r="N17" s="16" t="inlineStr"/>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr"/>
@@ -3046,14 +3001,14 @@
       </c>
       <c r="X17" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
+          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -3071,9 +3026,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E18" s="18" t="n">
-        <v>46281</v>
-      </c>
+      <c r="E18" s="18" t="n"/>
       <c r="F18" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -3093,7 +3046,7 @@
       <c r="N18" s="16" t="inlineStr"/>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
+          <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
@@ -3109,34 +3062,34 @@
         </is>
       </c>
       <c r="T18" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U18" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V18" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="W18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-06</t>
+          <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3152,31 +3105,51 @@
       <c r="E19" s="18" t="n"/>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>lsp</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
       <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="17" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
       <c r="L19" s="16" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
       <c r="N19" s="16" t="inlineStr"/>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>Yeah, that we will show you on the website.</t>
-        </is>
-      </c>
-      <c r="P19" s="16" t="inlineStr"/>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
       <c r="Q19" s="16" t="inlineStr"/>
       <c r="R19" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
       <c r="S19" s="17" t="inlineStr">
@@ -3185,29 +3158,29 @@
         </is>
       </c>
       <c r="T19" s="18" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
       <c r="X19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-03</t>
+          <t>2026-09-16-lsp-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -3217,7 +3190,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -3225,54 +3198,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E20" s="18" t="n"/>
+      <c r="E20" s="18" t="n">
+        <v>46276</v>
+      </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="16" t="inlineStr"/>
       <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>half-day</t>
-        </is>
-      </c>
+      <c r="K20" s="17" t="inlineStr"/>
       <c r="L20" s="16" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
+      <c r="M20" s="16" t="inlineStr"/>
       <c r="N20" s="16" t="inlineStr"/>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
-        </is>
-      </c>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr"/>
       <c r="Q20" s="16" t="inlineStr"/>
       <c r="R20" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S20" s="17" t="inlineStr">
@@ -3281,34 +3236,34 @@
         </is>
       </c>
       <c r="T20" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="U20" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W20" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-01</t>
+          <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3343,7 +3298,7 @@
       <c r="N21" s="16" t="inlineStr"/>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr"/>
@@ -3359,10 +3314,10 @@
         </is>
       </c>
       <c r="T21" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U21" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V21" s="18" t="n">
         <v>46276</v>
@@ -3374,19 +3329,19 @@
       </c>
       <c r="X21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
+          <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -3452,14 +3407,14 @@
       </c>
       <c r="X22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
+          <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
@@ -3478,7 +3433,7 @@
         </is>
       </c>
       <c r="E23" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -3499,7 +3454,7 @@
       <c r="N23" s="16" t="inlineStr"/>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr"/>
@@ -3515,34 +3470,34 @@
         </is>
       </c>
       <c r="T23" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Sarathchandra Babu</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3556,35 +3511,51 @@
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr"/>
-      <c r="I24" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>Send the poll to the team and collect responses.</t>
+        </is>
+      </c>
       <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="17" t="inlineStr"/>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
       <c r="L24" s="16" t="inlineStr"/>
       <c r="M24" s="16" t="inlineStr"/>
       <c r="N24" s="16" t="inlineStr"/>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr"/>
+          <t>Or, if you can put a poll in one of these, let's see here.</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t>D-2026-09-17-02</t>
+        </is>
+      </c>
       <c r="Q24" s="16" t="inlineStr"/>
       <c r="R24" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Code Apps Learning Curriculum Structure Discussion</t>
         </is>
       </c>
       <c r="S24" s="17" t="inlineStr">
@@ -3593,34 +3564,34 @@
         </is>
       </c>
       <c r="T24" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="W24" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
         </is>
       </c>
       <c r="X24" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-01</t>
+          <t>2026-09-17-unassigned-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Sarathchandra Babu</t>
+          <t>Adwaith</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -3633,33 +3604,31 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E25" s="18" t="n">
-        <v>46282</v>
-      </c>
+      <c r="E25" s="18" t="n"/>
       <c r="F25" s="16" t="inlineStr">
         <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
           <t>unassigned</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>unassigned</t>
-        </is>
-      </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>coordinate</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
-          <t>Send the poll to the team and collect responses.</t>
+          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
         </is>
       </c>
       <c r="J25" s="16" t="inlineStr"/>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L25" s="16" t="inlineStr"/>
@@ -3667,18 +3636,18 @@
       <c r="N25" s="16" t="inlineStr"/>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>Or, if you can put a poll in one of these, let's see here.</t>
+          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
         <is>
-          <t>D-2026-09-17-02</t>
+          <t>CR section 7.4 Notifications</t>
         </is>
       </c>
       <c r="Q25" s="16" t="inlineStr"/>
       <c r="R25" s="16" t="inlineStr">
         <is>
-          <t>Code Apps Learning Curriculum Structure Discussion</t>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
       <c r="S25" s="17" t="inlineStr">
@@ -3687,39 +3656,39 @@
         </is>
       </c>
       <c r="T25" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="W25" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
       <c r="X25" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-unassigned-01</t>
+          <t>2026-09-16-lsp-02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Adwaith</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
@@ -3727,10 +3696,12 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n"/>
+      <c r="E26" s="18" t="n">
+        <v>46283</v>
+      </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
@@ -3745,13 +3716,13 @@
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
-          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
+          <t>Write down the ideas after the walk</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr"/>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="L26" s="16" t="inlineStr"/>
@@ -3759,42 +3730,46 @@
       <c r="N26" s="16" t="inlineStr"/>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
+          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr">
         <is>
-          <t>CR section 7.4 Notifications</t>
-        </is>
-      </c>
-      <c r="Q26" s="16" t="inlineStr"/>
+          <t>line itself: personal walk brainstorm task</t>
+        </is>
+      </c>
+      <c r="Q26" s="16" t="inlineStr">
+        <is>
+          <t>basis unresolved</t>
+        </is>
+      </c>
       <c r="R26" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Personal note 2026-09-18</t>
         </is>
       </c>
       <c r="S26" s="17" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>unplanned</t>
         </is>
       </c>
       <c r="T26" s="18" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="U26" s="18" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="V26" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="W26" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>note-2026-09-18-walk-brainstorm.md</t>
         </is>
       </c>
       <c r="X26" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-02</t>
+          <t>2026-09-18-unassigned-01</t>
         </is>
       </c>
     </row>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -443,12 +443,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$11</f>
+              <f>'Dashboard'!$B$10:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$10:$C$11</f>
+              <f>'Dashboard'!$C$10:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -473,12 +473,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$11</f>
+              <f>'Dashboard'!$B$10:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$10:$D$11</f>
+              <f>'Dashboard'!$D$10:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$11</f>
+              <f>'Dashboard'!$B$10:$B$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$10:$E$11</f>
+              <f>'Dashboard'!$E$10:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -683,8 +683,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X27" headerRowCount="1">
-  <autoFilter ref="A1:X27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X35" headerRowCount="1">
+  <autoFilter ref="A1:X35"/>
   <tableColumns count="24">
     <tableColumn id="1" name="task"/>
     <tableColumn id="2" name="owner"/>
@@ -1036,7 +1036,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-21). Edits that should stick belong in the Google Sheet.</t>
+          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-24). Edits that should stick belong in the Google Sheet.</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C10" s="11">
@@ -1181,7 +1181,7 @@
     <row r="11">
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C11" s="11">
@@ -1206,29 +1206,83 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="C12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B12,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B13,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C12" s="14">
-        <f>SUM(C10:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="14">
-        <f>SUM(D10:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="14">
-        <f>SUM(E10:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="14">
-        <f>SUM(F10:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="14">
-        <f>SUM(G10:G11)</f>
+      <c r="C14" s="14">
+        <f>SUM(C10:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="14">
+        <f>SUM(D10:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>SUM(E10:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="14">
+        <f>SUM(F10:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="14">
+        <f>SUM(G10:G13)</f>
         <v/>
       </c>
     </row>
@@ -1560,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1714,17 +1768,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Verify and add date-based validation for inserting a new stage above or between existing stages in the plan tree.</t>
+          <t>Set and add the first demo date to the project plan.</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
@@ -1733,7 +1787,7 @@
         </is>
       </c>
       <c r="E2" s="18" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
@@ -1747,31 +1801,39 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>communicate</t>
         </is>
       </c>
       <c r="I2" s="16" t="inlineStr">
         <is>
-          <t>Add validation that checks a newly inserted stage's dates against neighboring stages' start/close dates.</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr"/>
+          <t>Confirm the demo date internally and message it to Sreekumar today.</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>Ashwini</t>
+        </is>
+      </c>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>15m</t>
         </is>
       </c>
       <c r="L2" s="16" t="inlineStr"/>
       <c r="M2" s="16" t="inlineStr"/>
-      <c r="N2" s="16" t="inlineStr"/>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-22: due 2026-09-21 -&gt; 2026-09-22 | 2026-09-22: Sreekumar repeated the demo-date ask after it was already 2 days overdue; Ashwini committed to share it today. Escalating to P1 per repeat-ask rule.</t>
+        </is>
+      </c>
       <c r="O2" s="16" t="inlineStr">
         <is>
-          <t>So, just okay, so we check that.</t>
+          <t>No, please put the date where we can have the first demo.</t>
         </is>
       </c>
       <c r="P2" s="16" t="inlineStr">
         <is>
-          <t>based on the dates, you have to get validation, cant be based on this date or the close date over here</t>
+          <t>2026-09-21-intelligent-tracker-03; repeated ask in this meeting</t>
         </is>
       </c>
       <c r="Q2" s="16" t="inlineStr"/>
@@ -1786,7 +1848,7 @@
         </is>
       </c>
       <c r="T2" s="18" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="U2" s="18" t="n"/>
       <c r="V2" s="18" t="n">
@@ -1799,73 +1861,75 @@
       </c>
       <c r="X2" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-01</t>
+          <t>2026-09-21-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Add a 'my tasks' filter to the plan tree so team members can see only the tasks assigned to them.</t>
+          <t>Implement CR time-block functionality once the Time Logs data structure is finalized.</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr"/>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
           <t>Laxmikant</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>intelligent-tracker</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>Implement a my-tasks filter option on the plan tree screen.</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr"/>
       <c r="K3" s="17" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L3" s="16" t="inlineStr"/>
-      <c r="M3" s="16" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>Time Logs module completion</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>Time Logs data structure/module completion</t>
+        </is>
+      </c>
       <c r="N3" s="16" t="inlineStr"/>
       <c r="O3" s="16" t="inlineStr">
         <is>
-          <t>Yes, yes, sir, we can give filters.</t>
-        </is>
-      </c>
-      <c r="P3" s="16" t="inlineStr">
-        <is>
-          <t>So my task or something like that, if you can give, that makes easy, you know, life easy for them.</t>
-        </is>
-      </c>
+          <t>functionality for that will not be done until the time logs is complete</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr"/>
       <c r="Q3" s="16" t="inlineStr"/>
       <c r="R3" s="16" t="inlineStr">
         <is>
@@ -1878,32 +1942,32 @@
         </is>
       </c>
       <c r="T3" s="18" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="U3" s="18" t="n"/>
       <c r="V3" s="18" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="W3" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-activity-tracker-sync.docx</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X3" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-02</t>
+          <t>2026-09-24-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Set and add the first demo date to the project plan.</t>
+          <t>Verify and add date-based validation for inserting a new stage above or between existing stages in the plan tree.</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1931,18 +1995,18 @@
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>coordinate</t>
+          <t>review</t>
         </is>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>Add the planned first-demo date to the project plan schedule.</t>
+          <t>Add validation that checks a newly inserted stage's dates against neighboring stages' start/close dates.</t>
         </is>
       </c>
       <c r="J4" s="16" t="inlineStr"/>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L4" s="16" t="inlineStr"/>
@@ -1950,12 +2014,12 @@
       <c r="N4" s="16" t="inlineStr"/>
       <c r="O4" s="16" t="inlineStr">
         <is>
-          <t>No, please put the date where we can have the first demo.</t>
+          <t>So, just okay, so we check that.</t>
         </is>
       </c>
       <c r="P4" s="16" t="inlineStr">
         <is>
-          <t>No, please put the date where we can have the first demo.</t>
+          <t>based on the dates, you have to get validation, cant be based on this date or the close date over here</t>
         </is>
       </c>
       <c r="Q4" s="16" t="inlineStr"/>
@@ -1983,33 +2047,33 @@
       </c>
       <c r="X4" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-03</t>
+          <t>2026-09-21-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Sign off on the reviewed database design after today's walkthrough.</t>
+          <t>Add a 'my tasks' filter to the plan tree so team members can see only the tasks assigned to them.</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -2021,19 +2085,35 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr"/>
-      <c r="I5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Implement a my-tasks filter option on the plan tree screen.</t>
+        </is>
+      </c>
       <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="17" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L5" s="16" t="inlineStr"/>
       <c r="M5" s="16" t="inlineStr"/>
       <c r="N5" s="16" t="inlineStr"/>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>I will be signing off on the Debi after the review</t>
-        </is>
-      </c>
-      <c r="P5" s="16" t="inlineStr"/>
+          <t>Yes, yes, sir, we can give filters.</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>So my task or something like that, if you can give, that makes easy, you know, life easy for them.</t>
+        </is>
+      </c>
       <c r="Q5" s="16" t="inlineStr"/>
       <c r="R5" s="16" t="inlineStr">
         <is>
@@ -2046,48 +2126,46 @@
         </is>
       </c>
       <c r="T5" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U5" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46286</v>
+      </c>
+      <c r="U5" s="18" t="n"/>
       <c r="V5" s="18" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="W5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-21-activity-tracker-sync.docx</t>
         </is>
       </c>
       <c r="X5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-01</t>
+          <t>2026-09-21-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Work with Ashwini on the overall workflow solution design document.</t>
+          <t>Share the full project plan through UAT with Sreekumar, including the date it will be available.</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E6" s="18" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
@@ -2099,23 +2177,39 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>communicate</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Confirm the full-plan-through-UAT availability date and send it to Sreekumar.</t>
+        </is>
+      </c>
       <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
       <c r="L6" s="16" t="inlineStr"/>
       <c r="M6" s="16" t="inlineStr"/>
       <c r="N6" s="16" t="inlineStr"/>
       <c r="O6" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi and I will be working on the proper workflow solution design</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr"/>
+          <t>I just want to go through the full plan of this application till UAT.</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>Sreekumar's request in this meeting</t>
+        </is>
+      </c>
       <c r="Q6" s="16" t="inlineStr"/>
       <c r="R6" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S6" s="17" t="inlineStr">
@@ -2124,48 +2218,46 @@
         </is>
       </c>
       <c r="T6" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U6" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U6" s="18" t="n"/>
       <c r="V6" s="18" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="W6" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X6" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-04</t>
+          <t>2026-09-22-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
+          <t>Build the checklist items and add-dependency screens in the plan tree.</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -2177,16 +2269,24 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr"/>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
       <c r="I7" s="16" t="inlineStr"/>
       <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="17" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L7" s="16" t="inlineStr"/>
       <c r="M7" s="16" t="inlineStr"/>
       <c r="N7" s="16" t="inlineStr"/>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>Change the UI. I'll change it.</t>
+          <t>Lakshmi will be working on what is it, checklist items and add dependency, whatever his screens</t>
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr"/>
@@ -2202,29 +2302,27 @@
         </is>
       </c>
       <c r="T7" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U7" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U7" s="18" t="n"/>
       <c r="V7" s="18" t="n">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="W7" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X7" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-05</t>
+          <t>2026-09-24-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
+          <t>Continue building the create functionality for the Change Request module.</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -2234,16 +2332,16 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -2255,16 +2353,24 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
       <c r="I8" s="16" t="inlineStr"/>
       <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="17" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L8" s="16" t="inlineStr"/>
       <c r="M8" s="16" t="inlineStr"/>
       <c r="N8" s="16" t="inlineStr"/>
       <c r="O8" s="16" t="inlineStr">
         <is>
-          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
+          <t>these Johan and Sam will be working on create functionality</t>
         </is>
       </c>
       <c r="P8" s="16" t="inlineStr"/>
@@ -2280,29 +2386,27 @@
         </is>
       </c>
       <c r="T8" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U8" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U8" s="18" t="n"/>
       <c r="V8" s="18" t="n">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="W8" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X8" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-06</t>
+          <t>2026-09-24-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
+          <t>Continue building the create functionality for the Issues module.</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -2312,16 +2416,16 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E9" s="18" t="n">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -2333,16 +2437,24 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr"/>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
       <c r="I9" s="16" t="inlineStr"/>
       <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="17" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L9" s="16" t="inlineStr"/>
       <c r="M9" s="16" t="inlineStr"/>
       <c r="N9" s="16" t="inlineStr"/>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>user stories you figure out and you show me</t>
+          <t>these Johan and Sam will be working on create functionality</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr"/>
@@ -2358,48 +2470,46 @@
         </is>
       </c>
       <c r="T9" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U9" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U9" s="18" t="n"/>
       <c r="V9" s="18" t="n">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="W9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-07</t>
+          <t>2026-09-24-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
+          <t>Send a group mail summarizing today's roadblocks.</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E10" s="18" t="n">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -2411,16 +2521,24 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr"/>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>communicate</t>
+        </is>
+      </c>
       <c r="I10" s="16" t="inlineStr"/>
       <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
       <c r="L10" s="16" t="inlineStr"/>
       <c r="M10" s="16" t="inlineStr"/>
       <c r="N10" s="16" t="inlineStr"/>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
+          <t>The road breaks are happening, then just, I'll put that in group mail, actually.</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr"/>
@@ -2436,48 +2554,46 @@
         </is>
       </c>
       <c r="T10" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U10" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U10" s="18" t="n"/>
       <c r="V10" s="18" t="n">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="W10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-01</t>
+          <t>2026-09-24-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
+          <t>Publish a weekly plan every Monday showing the team's planned activities and dates.</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -2489,27 +2605,39 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr"/>
-      <c r="I11" s="16" t="inlineStr"/>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>communicate</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Draft and share the first weekly plan covering the week starting September 28.</t>
+        </is>
+      </c>
       <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="17" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
       <c r="L11" s="16" t="inlineStr"/>
       <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
-        </is>
-      </c>
+      <c r="N11" s="16" t="inlineStr"/>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr"/>
+          <t>I want you to publish a weekly plan going forward from every Monday.</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>Sreekumar's directive in this meeting</t>
+        </is>
+      </c>
       <c r="Q11" s="16" t="inlineStr"/>
       <c r="R11" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S11" s="17" t="inlineStr">
@@ -2518,49 +2646,45 @@
         </is>
       </c>
       <c r="T11" s="18" t="n">
-        <v>46283</v>
-      </c>
-      <c r="U11" s="18" t="n">
-        <v>46283</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U11" s="18" t="n"/>
       <c r="V11" s="18" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="W11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-02</t>
+          <t>2026-09-22-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
+          <t>Add a rework checkbox to tasks created under an issue, defaulting to checked, editable per task by the TL or PM.</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>46281</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n"/>
       <c r="F12" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -2571,23 +2695,39 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr"/>
-      <c r="I12" s="16" t="inlineStr"/>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>Add the rework checkbox to the task creation form in the Issues module, default checked, with TL/PM override per task.</t>
+        </is>
+      </c>
       <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
       <c r="L12" s="16" t="inlineStr"/>
       <c r="M12" s="16" t="inlineStr"/>
       <c r="N12" s="16" t="inlineStr"/>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr"/>
+          <t>By default, let it be a rework, but the TL or the project manager can make it not a rework.</t>
+        </is>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>Sreekumar's rework checkbox decision in this meeting</t>
+        </is>
+      </c>
       <c r="Q12" s="16" t="inlineStr"/>
       <c r="R12" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S12" s="17" t="inlineStr">
@@ -2596,34 +2736,32 @@
         </is>
       </c>
       <c r="T12" s="18" t="n">
-        <v>46283</v>
-      </c>
-      <c r="U12" s="18" t="n">
-        <v>46283</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U12" s="18" t="n"/>
       <c r="V12" s="18" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="W12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-03</t>
+          <t>2026-09-22-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
+          <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -2637,7 +2775,7 @@
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -2658,7 +2796,7 @@
       <c r="N13" s="16" t="inlineStr"/>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
+          <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr"/>
@@ -2674,29 +2812,29 @@
         </is>
       </c>
       <c r="T13" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U13" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V13" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-04</t>
+          <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
+          <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -2715,7 +2853,7 @@
         </is>
       </c>
       <c r="E14" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -2736,7 +2874,7 @@
       <c r="N14" s="16" t="inlineStr"/>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
+          <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr"/>
@@ -2752,34 +2890,34 @@
         </is>
       </c>
       <c r="T14" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-05</t>
+          <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
+          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -2793,7 +2931,7 @@
         </is>
       </c>
       <c r="E15" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -2814,7 +2952,7 @@
       <c r="N15" s="16" t="inlineStr"/>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+          <t>Change the UI. I'll change it.</t>
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr"/>
@@ -2830,34 +2968,34 @@
         </is>
       </c>
       <c r="T15" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-07</t>
+          <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
+          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -2871,7 +3009,7 @@
         </is>
       </c>
       <c r="E16" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -2892,7 +3030,7 @@
       <c r="N16" s="16" t="inlineStr"/>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr"/>
@@ -2914,28 +3052,28 @@
         <v>46282</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-02</t>
+          <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
+          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -2949,7 +3087,7 @@
         </is>
       </c>
       <c r="E17" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -2970,7 +3108,7 @@
       <c r="N17" s="16" t="inlineStr"/>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
+          <t>user stories you figure out and you show me</t>
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr"/>
@@ -2992,28 +3130,28 @@
         <v>46282</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W17" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X17" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-06</t>
+          <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
+          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3026,7 +3164,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E18" s="18" t="n"/>
+      <c r="E18" s="18" t="n">
+        <v>46280</v>
+      </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -3046,7 +3186,7 @@
       <c r="N18" s="16" t="inlineStr"/>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>Yeah, that we will show you on the website.</t>
+          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
@@ -3062,10 +3202,10 @@
         </is>
       </c>
       <c r="T18" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U18" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V18" s="18" t="n">
         <v>46280</v>
@@ -3077,19 +3217,19 @@
       </c>
       <c r="X18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-03</t>
+          <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3102,54 +3242,40 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E19" s="18" t="n"/>
+      <c r="E19" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr"/>
       <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>half-day</t>
-        </is>
-      </c>
+      <c r="K19" s="17" t="inlineStr"/>
       <c r="L19" s="16" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
-      <c r="N19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
+        </is>
+      </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
-        </is>
-      </c>
-      <c r="P19" s="16" t="inlineStr">
-        <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
-        </is>
-      </c>
+          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr"/>
       <c r="Q19" s="16" t="inlineStr"/>
       <c r="R19" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S19" s="17" t="inlineStr">
@@ -3158,39 +3284,39 @@
         </is>
       </c>
       <c r="T19" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-01</t>
+          <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -3199,7 +3325,7 @@
         </is>
       </c>
       <c r="E20" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -3220,7 +3346,7 @@
       <c r="N20" s="16" t="inlineStr"/>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr"/>
@@ -3242,33 +3368,33 @@
         <v>46283</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
+          <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -3277,7 +3403,7 @@
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -3298,7 +3424,7 @@
       <c r="N21" s="16" t="inlineStr"/>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr"/>
@@ -3314,39 +3440,39 @@
         </is>
       </c>
       <c r="T21" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U21" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
@@ -3355,7 +3481,7 @@
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
@@ -3376,7 +3502,7 @@
       <c r="N22" s="16" t="inlineStr"/>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
       <c r="P22" s="16" t="inlineStr"/>
@@ -3392,39 +3518,39 @@
         </is>
       </c>
       <c r="T22" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
@@ -3454,7 +3580,7 @@
       <c r="N23" s="16" t="inlineStr"/>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr"/>
@@ -3485,24 +3611,24 @@
       </c>
       <c r="X23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-01</t>
+          <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Sarathchandra Babu</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
@@ -3511,51 +3637,35 @@
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>coordinate</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>Send the poll to the team and collect responses.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr"/>
+      <c r="I24" s="16" t="inlineStr"/>
       <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K24" s="17" t="inlineStr"/>
       <c r="L24" s="16" t="inlineStr"/>
       <c r="M24" s="16" t="inlineStr"/>
       <c r="N24" s="16" t="inlineStr"/>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>Or, if you can put a poll in one of these, let's see here.</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr">
-        <is>
-          <t>D-2026-09-17-02</t>
-        </is>
-      </c>
+          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr"/>
       <c r="Q24" s="16" t="inlineStr"/>
       <c r="R24" s="16" t="inlineStr">
         <is>
-          <t>Code Apps Learning Curriculum Structure Discussion</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S24" s="17" t="inlineStr">
@@ -3570,33 +3680,33 @@
         <v>46282</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="W24" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X24" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-unassigned-01</t>
+          <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Adwaith</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D25" s="17" t="inlineStr">
@@ -3604,50 +3714,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E25" s="18" t="n"/>
+      <c r="E25" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr"/>
+      <c r="I25" s="16" t="inlineStr"/>
       <c r="J25" s="16" t="inlineStr"/>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K25" s="17" t="inlineStr"/>
       <c r="L25" s="16" t="inlineStr"/>
       <c r="M25" s="16" t="inlineStr"/>
       <c r="N25" s="16" t="inlineStr"/>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>CR section 7.4 Notifications</t>
-        </is>
-      </c>
+          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr"/>
       <c r="Q25" s="16" t="inlineStr"/>
       <c r="R25" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S25" s="17" t="inlineStr">
@@ -3656,39 +3752,39 @@
         </is>
       </c>
       <c r="T25" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="V25" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="W25" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X25" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-02</t>
+          <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
@@ -3696,87 +3792,65 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n">
-        <v>46283</v>
-      </c>
+      <c r="E26" s="18" t="n"/>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>Write down the ideas after the walk</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr"/>
+      <c r="I26" s="16" t="inlineStr"/>
       <c r="J26" s="16" t="inlineStr"/>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K26" s="17" t="inlineStr"/>
       <c r="L26" s="16" t="inlineStr"/>
       <c r="M26" s="16" t="inlineStr"/>
       <c r="N26" s="16" t="inlineStr"/>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
-        </is>
-      </c>
-      <c r="P26" s="16" t="inlineStr">
-        <is>
-          <t>line itself: personal walk brainstorm task</t>
-        </is>
-      </c>
-      <c r="Q26" s="16" t="inlineStr">
-        <is>
-          <t>basis unresolved</t>
-        </is>
-      </c>
+          <t>Yeah, that we will show you on the website.</t>
+        </is>
+      </c>
+      <c r="P26" s="16" t="inlineStr"/>
+      <c r="Q26" s="16" t="inlineStr"/>
       <c r="R26" s="16" t="inlineStr">
         <is>
-          <t>Personal note 2026-09-18</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S26" s="17" t="inlineStr">
         <is>
-          <t>unplanned</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="T26" s="18" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="U26" s="18" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="V26" s="18" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="W26" s="16" t="inlineStr">
         <is>
-          <t>note-2026-09-18-walk-brainstorm.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X26" s="16" t="inlineStr">
         <is>
-          <t>2026-09-18-unassigned-01</t>
+          <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
@@ -3786,7 +3860,7 @@
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -3807,31 +3881,35 @@
       </c>
       <c r="H27" s="16" t="inlineStr">
         <is>
-          <t>decide</t>
+          <t>review</t>
         </is>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr"/>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>half-day</t>
         </is>
       </c>
       <c r="L27" s="16" t="inlineStr"/>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
       <c r="N27" s="16" t="inlineStr"/>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>Agree a retention or archival policy for closed periodic closures.</t>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr">
         <is>
-          <t>CR section 8.6 Sizing</t>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
         </is>
       </c>
       <c r="Q27" s="16" t="inlineStr"/>
@@ -3860,6 +3938,694 @@
         </is>
       </c>
       <c r="X27" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr"/>
+      <c r="I28" s="16" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr"/>
+      <c r="K28" s="17" t="inlineStr"/>
+      <c r="L28" s="16" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr"/>
+      <c r="N28" s="16" t="inlineStr"/>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+        </is>
+      </c>
+      <c r="P28" s="16" t="inlineStr"/>
+      <c r="Q28" s="16" t="inlineStr"/>
+      <c r="R28" s="16" t="inlineStr">
+        <is>
+          <t>Activity Tracker internal sync-up</t>
+        </is>
+      </c>
+      <c r="S28" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T28" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="U28" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="V28" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="W28" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="X28" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11-intelligent-tracker-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Johan</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr"/>
+      <c r="I29" s="16" t="inlineStr"/>
+      <c r="J29" s="16" t="inlineStr"/>
+      <c r="K29" s="17" t="inlineStr"/>
+      <c r="L29" s="16" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr"/>
+      <c r="N29" s="16" t="inlineStr"/>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="inlineStr"/>
+      <c r="Q29" s="16" t="inlineStr"/>
+      <c r="R29" s="16" t="inlineStr">
+        <is>
+          <t>Activity Tracker internal sync-up</t>
+        </is>
+      </c>
+      <c r="S29" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T29" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U29" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="V29" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="W29" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="X29" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11-intelligent-tracker-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr"/>
+      <c r="J30" s="16" t="inlineStr"/>
+      <c r="K30" s="17" t="inlineStr"/>
+      <c r="L30" s="16" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr"/>
+      <c r="N30" s="16" t="inlineStr"/>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr"/>
+      <c r="Q30" s="16" t="inlineStr"/>
+      <c r="R30" s="16" t="inlineStr">
+        <is>
+          <t>Activity Tracker internal sync-up</t>
+        </is>
+      </c>
+      <c r="S30" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T30" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U30" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="V30" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="W30" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="X30" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-11-intelligent-tracker-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>intelligent-tracker</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr"/>
+      <c r="I31" s="16" t="inlineStr"/>
+      <c r="J31" s="16" t="inlineStr"/>
+      <c r="K31" s="17" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr"/>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr"/>
+      <c r="Q31" s="16" t="inlineStr"/>
+      <c r="R31" s="16" t="inlineStr">
+        <is>
+          <t>Activity Tracker internal sync-up</t>
+        </is>
+      </c>
+      <c r="S31" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T31" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="U31" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="V31" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W31" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="X31" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-intelligent-tracker-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Sarathchandra Babu</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>Send the poll to the team and collect responses.</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr"/>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr"/>
+      <c r="N32" s="16" t="inlineStr"/>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>Or, if you can put a poll in one of these, let's see here.</t>
+        </is>
+      </c>
+      <c r="P32" s="16" t="inlineStr">
+        <is>
+          <t>D-2026-09-17-02</t>
+        </is>
+      </c>
+      <c r="Q32" s="16" t="inlineStr"/>
+      <c r="R32" s="16" t="inlineStr">
+        <is>
+          <t>Code Apps Learning Curriculum Structure Discussion</t>
+        </is>
+      </c>
+      <c r="S32" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T32" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U32" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="V32" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="W32" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+        </is>
+      </c>
+      <c r="X32" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-17-unassigned-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Adwaith</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr"/>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr"/>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
+        </is>
+      </c>
+      <c r="P33" s="16" t="inlineStr">
+        <is>
+          <t>CR section 7.4 Notifications</t>
+        </is>
+      </c>
+      <c r="Q33" s="16" t="inlineStr"/>
+      <c r="R33" s="16" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="S33" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T33" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U33" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V33" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W33" s="16" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="X33" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Write down the ideas after the walk</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr"/>
+      <c r="K34" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr"/>
+      <c r="N34" s="16" t="inlineStr"/>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
+        </is>
+      </c>
+      <c r="P34" s="16" t="inlineStr">
+        <is>
+          <t>line itself: personal walk brainstorm task</t>
+        </is>
+      </c>
+      <c r="Q34" s="16" t="inlineStr">
+        <is>
+          <t>basis unresolved</t>
+        </is>
+      </c>
+      <c r="R34" s="16" t="inlineStr">
+        <is>
+          <t>Personal note 2026-09-18</t>
+        </is>
+      </c>
+      <c r="S34" s="17" t="inlineStr">
+        <is>
+          <t>unplanned</t>
+        </is>
+      </c>
+      <c r="T34" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="U34" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="V34" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="W34" s="16" t="inlineStr">
+        <is>
+          <t>note-2026-09-18-walk-brainstorm.md</t>
+        </is>
+      </c>
+      <c r="X34" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-18-unassigned-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr"/>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr"/>
+      <c r="O35" s="16" t="inlineStr">
+        <is>
+          <t>Agree a retention or archival policy for closed periodic closures.</t>
+        </is>
+      </c>
+      <c r="P35" s="16" t="inlineStr">
+        <is>
+          <t>CR section 8.6 Sizing</t>
+        </is>
+      </c>
+      <c r="Q35" s="16" t="inlineStr"/>
+      <c r="R35" s="16" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="S35" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T35" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U35" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V35" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W35" s="16" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="X35" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -443,12 +443,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$13</f>
+              <f>'Dashboard'!$B$10:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$10:$C$13</f>
+              <f>'Dashboard'!$C$10:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -473,12 +473,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$13</f>
+              <f>'Dashboard'!$B$10:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$10:$D$13</f>
+              <f>'Dashboard'!$D$10:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -503,12 +503,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$10:$B$13</f>
+              <f>'Dashboard'!$B$10:$B$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$10:$E$13</f>
+              <f>'Dashboard'!$E$10:$E$15</f>
             </numRef>
           </val>
         </ser>
@@ -642,7 +642,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="1944000"/>
+    <ext cx="5760000" cy="2340000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -683,8 +683,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X35" headerRowCount="1">
-  <autoFilter ref="A1:X35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actions" displayName="Actions" ref="A1:X39" headerRowCount="1">
+  <autoFilter ref="A1:X39"/>
   <tableColumns count="24">
     <tableColumn id="1" name="task"/>
     <tableColumn id="2" name="owner"/>
@@ -1036,7 +1036,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-24). Edits that should stick belong in the Google Sheet.</t>
+          <t>Live: every number is a formula over the Actions sheet, so a status changed there moves this page at once. Owner and project lists refresh on each run (last 2026-09-25). Edits that should stick belong in the Google Sheet.</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
     <row r="12">
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C12" s="11">
@@ -1235,7 +1235,7 @@
     <row r="13">
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C13" s="11">
@@ -1260,29 +1260,83 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="C14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B14,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Thenappan</t>
+        </is>
+      </c>
+      <c r="C15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$C$2:$C$5000,"P1"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$C$2:$C$5000,"P2"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$C$2:$C$5000,"P3"))</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>SUMPRODUCT(COUNTIFS(Actions!$D$2:$D$5000,{"blocked","in_progress","open","to_verify"},Actions!$B$2:$B$5000,$B15,Actions!$E$2:$E$5000,"&lt;"&amp;TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C14" s="14">
-        <f>SUM(C10:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>SUM(D10:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>SUM(E10:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
-        <f>SUM(F10:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>SUM(G10:G13)</f>
+      <c r="C16" s="14">
+        <f>SUM(C10:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="14">
+        <f>SUM(D10:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>SUM(E10:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>SUM(F10:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>SUM(G10:G15)</f>
         <v/>
       </c>
     </row>
@@ -1614,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1783,7 +1837,7 @@
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>to_verify</t>
         </is>
       </c>
       <c r="E2" s="18" t="n">
@@ -1823,7 +1877,7 @@
       <c r="M2" s="16" t="inlineStr"/>
       <c r="N2" s="16" t="inlineStr">
         <is>
-          <t>2026-09-22: due 2026-09-21 -&gt; 2026-09-22 | 2026-09-22: Sreekumar repeated the demo-date ask after it was already 2 days overdue; Ashwini committed to share it today. Escalating to P1 per repeat-ask rule.</t>
+          <t>2026-09-22: due 2026-09-21 -&gt; 2026-09-22 | 2026-09-22: Sreekumar repeated the demo-date ask after it was already 2 days overdue; Ashwini committed to share it today. Escalating to P1 per repeat-ask rule. | 2026-09-25: Ashwini confirmed demo dates: Issues+CR demo next Wednesday (2026-09-30), Plan Tree demo on 2026-10-05; date already shared with Sreekumar. [I have shared you, sir, like maybe it's 9th, 5th, 9th of October, I guess, sorry, 5th of October, sir.]</t>
         </is>
       </c>
       <c r="O2" s="16" t="inlineStr">
@@ -1833,10 +1887,14 @@
       </c>
       <c r="P2" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-03; repeated ask in this meeting</t>
-        </is>
-      </c>
-      <c r="Q2" s="16" t="inlineStr"/>
+          <t>2026-09-21-intelligent-tracker-03</t>
+        </is>
+      </c>
+      <c r="Q2" s="16" t="inlineStr">
+        <is>
+          <t>due before meeting: 2026-09-22</t>
+        </is>
+      </c>
       <c r="R2" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
@@ -1848,7 +1906,7 @@
         </is>
       </c>
       <c r="T2" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="U2" s="18" t="n"/>
       <c r="V2" s="18" t="n">
@@ -2574,12 +2632,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Publish a weekly plan every Monday showing the team's planned activities and dates.</t>
+          <t>Review the CAPA workflow document comparing Azure DevOps, Viva Vault and SAP in detail.</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2593,32 +2651,28 @@
         </is>
       </c>
       <c r="E11" s="18" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>communicate</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>Draft and share the first weekly plan covering the week starting September 28.</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr"/>
       <c r="J11" s="16" t="inlineStr"/>
       <c r="K11" s="17" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L11" s="16" t="inlineStr"/>
@@ -2626,18 +2680,18 @@
       <c r="N11" s="16" t="inlineStr"/>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>I want you to publish a weekly plan going forward from every Monday.</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr">
-        <is>
-          <t>Sreekumar's directive in this meeting</t>
-        </is>
-      </c>
-      <c r="Q11" s="16" t="inlineStr"/>
+          <t>even I have to go through this workflow in detail</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr">
+        <is>
+          <t>owner unknown: Aswin</t>
+        </is>
+      </c>
       <c r="R11" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up (2026-09-22)</t>
+          <t>CAPA - Discussion On Existing System's</t>
         </is>
       </c>
       <c r="S11" s="17" t="inlineStr">
@@ -2646,32 +2700,32 @@
         </is>
       </c>
       <c r="T11" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="U11" s="18" t="n"/>
       <c r="V11" s="18" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="W11" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker-Internal Sync-up.docx</t>
+          <t>CAPA - Discussion On Existing System's .docx</t>
         </is>
       </c>
       <c r="X11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-22-intelligent-tracker-01</t>
+          <t>2026-09-25-unassigned-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Add a rework checkbox to tasks created under an issue, defaulting to checked, editable per task by the TL or PM.</t>
+          <t>Check off items on the shared list comparing existing CAPA systems.</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Thenappan</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2684,31 +2738,29 @@
           <t>open</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n"/>
+      <c r="E12" s="18" t="n">
+        <v>46290</v>
+      </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>Add the rework checkbox to the task creation form in the Issues module, default checked, with TL/PM override per task.</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr"/>
       <c r="J12" s="16" t="inlineStr"/>
       <c r="K12" s="17" t="inlineStr">
         <is>
-          <t>half-day</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L12" s="16" t="inlineStr"/>
@@ -2716,18 +2768,18 @@
       <c r="N12" s="16" t="inlineStr"/>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>By default, let it be a rework, but the TL or the project manager can make it not a rework.</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr">
-        <is>
-          <t>Sreekumar's rework checkbox decision in this meeting</t>
-        </is>
-      </c>
-      <c r="Q12" s="16" t="inlineStr"/>
+          <t>So I'll just cheque it off</t>
+        </is>
+      </c>
+      <c r="P12" s="16" t="inlineStr"/>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>owner unknown: Thenappan</t>
+        </is>
+      </c>
       <c r="R12" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up (2026-09-22)</t>
+          <t>CAPA - Discussion On Existing System's</t>
         </is>
       </c>
       <c r="S12" s="17" t="inlineStr">
@@ -2736,74 +2788,86 @@
         </is>
       </c>
       <c r="T12" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="U12" s="18" t="n"/>
       <c r="V12" s="18" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="W12" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker-Internal Sync-up.docx</t>
+          <t>CAPA - Discussion On Existing System's .docx</t>
         </is>
       </c>
       <c r="X12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-22-intelligent-tracker-03</t>
+          <t>2026-09-25-unassigned-02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Sign off on the reviewed database design after today's walkthrough.</t>
+          <t>Add newly identified system-comparison items to the shared Excel file with Thenappan.</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
       <c r="I13" s="16" t="inlineStr"/>
       <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L13" s="16" t="inlineStr"/>
       <c r="M13" s="16" t="inlineStr"/>
       <c r="N13" s="16" t="inlineStr"/>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>I will be signing off on the Debi after the review</t>
+          <t>we can get a few more things, then we will add it in the same Excel</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr">
+        <is>
+          <t>owner unknown: Aswin</t>
+        </is>
+      </c>
       <c r="R13" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CAPA - Discussion On Existing System's</t>
         </is>
       </c>
       <c r="S13" s="17" t="inlineStr">
@@ -2812,48 +2876,46 @@
         </is>
       </c>
       <c r="T13" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U13" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="U13" s="18" t="n"/>
       <c r="V13" s="18" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="W13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>CAPA - Discussion On Existing System's .docx</t>
         </is>
       </c>
       <c r="X13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-01</t>
+          <t>2026-09-25-unassigned-03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Work with Ashwini on the overall workflow solution design document.</t>
+          <t>Publish a weekly plan every Monday showing the team's planned activities and dates.</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E14" s="18" t="n">
-        <v>46276</v>
+        <v>46293</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -2865,23 +2927,39 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr"/>
-      <c r="I14" s="16" t="inlineStr"/>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>communicate</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>Draft and share the first weekly plan covering the week starting September 28.</t>
+        </is>
+      </c>
       <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="17" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
       <c r="L14" s="16" t="inlineStr"/>
       <c r="M14" s="16" t="inlineStr"/>
       <c r="N14" s="16" t="inlineStr"/>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi and I will be working on the proper workflow solution design</t>
-        </is>
-      </c>
-      <c r="P14" s="16" t="inlineStr"/>
+          <t>I want you to publish a weekly plan going forward from every Monday.</t>
+        </is>
+      </c>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t>Sreekumar's directive in this meeting</t>
+        </is>
+      </c>
       <c r="Q14" s="16" t="inlineStr"/>
       <c r="R14" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S14" s="17" t="inlineStr">
@@ -2890,49 +2968,45 @@
         </is>
       </c>
       <c r="T14" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U14" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U14" s="18" t="n"/>
       <c r="V14" s="18" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="W14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-04</t>
+          <t>2026-09-22-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
+          <t>Add a rework checkbox to tasks created under an issue, defaulting to checked, editable per task by the TL or PM.</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>46276</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -2943,23 +3017,39 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>Add the rework checkbox to the task creation form in the Issues module, default checked, with TL/PM override per task.</t>
+        </is>
+      </c>
       <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="17" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
       <c r="L15" s="16" t="inlineStr"/>
       <c r="M15" s="16" t="inlineStr"/>
       <c r="N15" s="16" t="inlineStr"/>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>Change the UI. I'll change it.</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr"/>
+          <t>By default, let it be a rework, but the TL or the project manager can make it not a rework.</t>
+        </is>
+      </c>
+      <c r="P15" s="16" t="inlineStr">
+        <is>
+          <t>Sreekumar's rework checkbox decision in this meeting</t>
+        </is>
+      </c>
       <c r="Q15" s="16" t="inlineStr"/>
       <c r="R15" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S15" s="17" t="inlineStr">
@@ -2968,76 +3058,84 @@
         </is>
       </c>
       <c r="T15" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U15" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="U15" s="18" t="n"/>
       <c r="V15" s="18" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="W15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-05</t>
+          <t>2026-09-22-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
+          <t>Decide with Thenappan which existing system approach is best and report the choice to the team.</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>46276</v>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n"/>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>decide</t>
+        </is>
+      </c>
       <c r="I16" s="16" t="inlineStr"/>
       <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="17" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L16" s="16" t="inlineStr"/>
       <c r="M16" s="16" t="inlineStr"/>
       <c r="N16" s="16" t="inlineStr"/>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
+          <t>In time, I will update, which I feel is better, OK</t>
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr"/>
-      <c r="Q16" s="16" t="inlineStr"/>
+      <c r="Q16" s="16" t="inlineStr">
+        <is>
+          <t>owner unknown: Aswin</t>
+        </is>
+      </c>
       <c r="R16" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CAPA - Discussion On Existing System's</t>
         </is>
       </c>
       <c r="S16" s="17" t="inlineStr">
@@ -3046,34 +3144,32 @@
         </is>
       </c>
       <c r="T16" s="18" t="n">
-        <v>46282</v>
-      </c>
-      <c r="U16" s="18" t="n">
-        <v>46282</v>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="U16" s="18" t="n"/>
       <c r="V16" s="18" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="W16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>CAPA - Discussion On Existing System's .docx</t>
         </is>
       </c>
       <c r="X16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-06</t>
+          <t>2026-09-25-unassigned-04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
+          <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3108,7 +3204,7 @@
       <c r="N17" s="16" t="inlineStr"/>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>user stories you figure out and you show me</t>
+          <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr"/>
@@ -3139,14 +3235,14 @@
       </c>
       <c r="X17" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-07</t>
+          <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
+          <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -3165,7 +3261,7 @@
         </is>
       </c>
       <c r="E18" s="18" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -3186,7 +3282,7 @@
       <c r="N18" s="16" t="inlineStr"/>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
+          <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
@@ -3208,28 +3304,28 @@
         <v>46282</v>
       </c>
       <c r="V18" s="18" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="W18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-01</t>
+          <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
+          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -3243,7 +3339,7 @@
         </is>
       </c>
       <c r="E19" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -3261,14 +3357,10 @@
       <c r="K19" s="17" t="inlineStr"/>
       <c r="L19" s="16" t="inlineStr"/>
       <c r="M19" s="16" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
-        </is>
-      </c>
+      <c r="N19" s="16" t="inlineStr"/>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
+          <t>Change the UI. I'll change it.</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr"/>
@@ -3284,29 +3376,29 @@
         </is>
       </c>
       <c r="T19" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U19" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V19" s="18" t="n">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-02</t>
+          <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
+          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -3325,7 +3417,7 @@
         </is>
       </c>
       <c r="E20" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -3346,7 +3438,7 @@
       <c r="N20" s="16" t="inlineStr"/>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
+          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr"/>
@@ -3362,34 +3454,34 @@
         </is>
       </c>
       <c r="T20" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U20" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-03</t>
+          <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
+          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3403,7 +3495,7 @@
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -3424,7 +3516,7 @@
       <c r="N21" s="16" t="inlineStr"/>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
+          <t>user stories you figure out and you show me</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr"/>
@@ -3440,29 +3532,29 @@
         </is>
       </c>
       <c r="T21" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U21" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-04</t>
+          <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
+          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
@@ -3481,7 +3573,7 @@
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
@@ -3502,7 +3594,7 @@
       <c r="N22" s="16" t="inlineStr"/>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
+          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
       <c r="P22" s="16" t="inlineStr"/>
@@ -3518,34 +3610,34 @@
         </is>
       </c>
       <c r="T22" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="W22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-05</t>
+          <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
+          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -3577,10 +3669,14 @@
       <c r="K23" s="17" t="inlineStr"/>
       <c r="L23" s="16" t="inlineStr"/>
       <c r="M23" s="16" t="inlineStr"/>
-      <c r="N23" s="16" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
+        </is>
+      </c>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr"/>
@@ -3602,28 +3698,28 @@
         <v>46283</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="W23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-07</t>
+          <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
+          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3658,7 +3754,7 @@
       <c r="N24" s="16" t="inlineStr"/>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
       <c r="P24" s="16" t="inlineStr"/>
@@ -3674,10 +3770,10 @@
         </is>
       </c>
       <c r="T24" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V24" s="18" t="n">
         <v>46281</v>
@@ -3689,19 +3785,19 @@
       </c>
       <c r="X24" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
+          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -3736,7 +3832,7 @@
       <c r="N25" s="16" t="inlineStr"/>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
+          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr"/>
@@ -3752,10 +3848,10 @@
         </is>
       </c>
       <c r="T25" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V25" s="18" t="n">
         <v>46281</v>
@@ -3767,19 +3863,19 @@
       </c>
       <c r="X25" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-06</t>
+          <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
+          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -3792,7 +3888,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n"/>
+      <c r="E26" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -3812,7 +3910,7 @@
       <c r="N26" s="16" t="inlineStr"/>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>Yeah, that we will show you on the website.</t>
+          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr"/>
@@ -3834,23 +3932,23 @@
         <v>46283</v>
       </c>
       <c r="V26" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="W26" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X26" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
+          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
@@ -3868,54 +3966,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E27" s="18" t="n"/>
+      <c r="E27" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr"/>
+      <c r="I27" s="16" t="inlineStr"/>
       <c r="J27" s="16" t="inlineStr"/>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>half-day</t>
-        </is>
-      </c>
+      <c r="K27" s="17" t="inlineStr"/>
       <c r="L27" s="16" t="inlineStr"/>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>List of new columns/tables from this CR</t>
-        </is>
-      </c>
+      <c r="M27" s="16" t="inlineStr"/>
       <c r="N27" s="16" t="inlineStr"/>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
-        </is>
-      </c>
-      <c r="P27" s="16" t="inlineStr">
-        <is>
-          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
-        </is>
-      </c>
+          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+        </is>
+      </c>
+      <c r="P27" s="16" t="inlineStr"/>
       <c r="Q27" s="16" t="inlineStr"/>
       <c r="R27" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S27" s="17" t="inlineStr">
@@ -3924,39 +4004,39 @@
         </is>
       </c>
       <c r="T27" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="V27" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="W27" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X27" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-01</t>
+          <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
+          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
@@ -3965,7 +4045,7 @@
         </is>
       </c>
       <c r="E28" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
@@ -3986,7 +4066,7 @@
       <c r="N28" s="16" t="inlineStr"/>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
       <c r="P28" s="16" t="inlineStr"/>
@@ -4002,39 +4082,39 @@
         </is>
       </c>
       <c r="T28" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U28" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V28" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W28" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X28" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-08</t>
+          <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D29" s="17" t="inlineStr">
@@ -4043,7 +4123,7 @@
         </is>
       </c>
       <c r="E29" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -4064,7 +4144,7 @@
       <c r="N29" s="16" t="inlineStr"/>
       <c r="O29" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
       <c r="P29" s="16" t="inlineStr"/>
@@ -4086,33 +4166,33 @@
         <v>46282</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="W29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
+          <t>Show Sreekumar in the application how CR items and issues resolve into work-item tasks.</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
@@ -4120,9 +4200,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E30" s="18" t="n">
-        <v>46276</v>
-      </c>
+      <c r="E30" s="18" t="n"/>
       <c r="F30" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -4142,7 +4220,7 @@
       <c r="N30" s="16" t="inlineStr"/>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+          <t>Yeah, that we will show you on the website.</t>
         </is>
       </c>
       <c r="P30" s="16" t="inlineStr"/>
@@ -4158,39 +4236,39 @@
         </is>
       </c>
       <c r="T30" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U30" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V30" s="18" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="W30" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X30" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-03</t>
+          <t>2026-09-15-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
+          <t>Review the new lsp_claim_line_items table and added claim-table columns against the no-further-master-data-changes position agreed with Adwaith.</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
@@ -4198,36 +4276,54 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E31" s="18" t="n">
-        <v>46281</v>
-      </c>
+      <c r="E31" s="18" t="n"/>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>lsp</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr"/>
-      <c r="I31" s="16" t="inlineStr"/>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>Ayush compares the new tables and columns against the sign-off position and flags any conflicts to Adwaith.</t>
+        </is>
+      </c>
       <c r="J31" s="16" t="inlineStr"/>
-      <c r="K31" s="17" t="inlineStr"/>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>half-day</t>
+        </is>
+      </c>
       <c r="L31" s="16" t="inlineStr"/>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>List of new columns/tables from this CR</t>
+        </is>
+      </c>
       <c r="N31" s="16" t="inlineStr"/>
       <c r="O31" s="16" t="inlineStr">
         <is>
-          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
-        </is>
-      </c>
-      <c r="P31" s="16" t="inlineStr"/>
+          <t>Existing claim table: add lsp_fy, lsp_totalnrclaimwithsr, lsp_totalpoclaimwithsr, plus the status-sync fields</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr">
+        <is>
+          <t>No further master data or DB column changes after sign-off (told to Adwaith on 2026-09-16).</t>
+        </is>
+      </c>
       <c r="Q31" s="16" t="inlineStr"/>
       <c r="R31" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
         </is>
       </c>
       <c r="S31" s="17" t="inlineStr">
@@ -4236,34 +4332,34 @@
         </is>
       </c>
       <c r="T31" s="18" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="U31" s="18" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="V31" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="W31" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
       <c r="X31" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-01</t>
+          <t>2026-09-16-lsp-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+          <t>Speak with Laxmikant to plan the development plan and model for the build.</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>Sarathchandra Babu</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
@@ -4277,51 +4373,35 @@
         </is>
       </c>
       <c r="E32" s="18" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>coordinate</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>Send the poll to the team and collect responses.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr"/>
+      <c r="I32" s="16" t="inlineStr"/>
       <c r="J32" s="16" t="inlineStr"/>
-      <c r="K32" s="17" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K32" s="17" t="inlineStr"/>
       <c r="L32" s="16" t="inlineStr"/>
       <c r="M32" s="16" t="inlineStr"/>
       <c r="N32" s="16" t="inlineStr"/>
       <c r="O32" s="16" t="inlineStr">
         <is>
-          <t>Or, if you can put a poll in one of these, let's see here.</t>
-        </is>
-      </c>
-      <c r="P32" s="16" t="inlineStr">
-        <is>
-          <t>D-2026-09-17-02</t>
-        </is>
-      </c>
+          <t>I will speak to Lakshmi, plan development plan with model that's it</t>
+        </is>
+      </c>
+      <c r="P32" s="16" t="inlineStr"/>
       <c r="Q32" s="16" t="inlineStr"/>
       <c r="R32" s="16" t="inlineStr">
         <is>
-          <t>Code Apps Learning Curriculum Structure Discussion</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S32" s="17" t="inlineStr">
@@ -4330,34 +4410,34 @@
         </is>
       </c>
       <c r="T32" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U32" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V32" s="18" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="W32" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X32" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17-unassigned-01</t>
+          <t>2026-09-11-intelligent-tracker-08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+          <t>Log detailed CR module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Adwaith</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -4370,50 +4450,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E33" s="18" t="n"/>
+      <c r="E33" s="18" t="n">
+        <v>46276</v>
+      </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr"/>
+      <c r="I33" s="16" t="inlineStr"/>
       <c r="J33" s="16" t="inlineStr"/>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K33" s="17" t="inlineStr"/>
       <c r="L33" s="16" t="inlineStr"/>
       <c r="M33" s="16" t="inlineStr"/>
       <c r="N33" s="16" t="inlineStr"/>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
-        </is>
-      </c>
-      <c r="P33" s="16" t="inlineStr">
-        <is>
-          <t>CR section 7.4 Notifications</t>
-        </is>
-      </c>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P33" s="16" t="inlineStr"/>
       <c r="Q33" s="16" t="inlineStr"/>
       <c r="R33" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S33" s="17" t="inlineStr">
@@ -4422,39 +4488,39 @@
         </is>
       </c>
       <c r="T33" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="U33" s="18" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="V33" s="18" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="W33" s="16" t="inlineStr">
         <is>
-          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X33" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-lsp-02</t>
+          <t>2026-09-11-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+          <t>Log detailed Issues module tasks for today in Zoho and send the task ID to Ashwini.</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -4463,96 +4529,76 @@
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>Write down the ideas after the walk</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr"/>
+      <c r="I34" s="16" t="inlineStr"/>
       <c r="J34" s="16" t="inlineStr"/>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
+      <c r="K34" s="17" t="inlineStr"/>
       <c r="L34" s="16" t="inlineStr"/>
       <c r="M34" s="16" t="inlineStr"/>
       <c r="N34" s="16" t="inlineStr"/>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
-        </is>
-      </c>
-      <c r="P34" s="16" t="inlineStr">
-        <is>
-          <t>line itself: personal walk brainstorm task</t>
-        </is>
-      </c>
-      <c r="Q34" s="16" t="inlineStr">
-        <is>
-          <t>basis unresolved</t>
-        </is>
-      </c>
+          <t>they will be noting down their detailed task in Zoho and giving a Task ID to Ashwini</t>
+        </is>
+      </c>
+      <c r="P34" s="16" t="inlineStr"/>
+      <c r="Q34" s="16" t="inlineStr"/>
       <c r="R34" s="16" t="inlineStr">
         <is>
-          <t>Personal note 2026-09-18</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S34" s="17" t="inlineStr">
         <is>
-          <t>unplanned</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="T34" s="18" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="U34" s="18" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="V34" s="18" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="W34" s="16" t="inlineStr">
         <is>
-          <t>note-2026-09-18-walk-brainstorm.md</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X34" s="16" t="inlineStr">
         <is>
-          <t>2026-09-18-unassigned-01</t>
+          <t>2026-09-11-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+          <t>Discuss with Laxmikant the feasibility and structural changes needed for the new issue fields from Sreekumar's design before building them.</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
@@ -4560,50 +4606,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E35" s="18" t="n"/>
+      <c r="E35" s="18" t="n">
+        <v>46281</v>
+      </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>lsp</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>decide</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr"/>
+      <c r="I35" s="16" t="inlineStr"/>
       <c r="J35" s="16" t="inlineStr"/>
-      <c r="K35" s="17" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K35" s="17" t="inlineStr"/>
       <c r="L35" s="16" t="inlineStr"/>
       <c r="M35" s="16" t="inlineStr"/>
       <c r="N35" s="16" t="inlineStr"/>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>Agree a retention or archival policy for closed periodic closures.</t>
-        </is>
-      </c>
-      <c r="P35" s="16" t="inlineStr">
-        <is>
-          <t>CR section 8.6 Sizing</t>
-        </is>
-      </c>
+          <t>I wanted Sam to talk to you regarding the feasibility of that. I know it will work, but what is the structure change?</t>
+        </is>
+      </c>
+      <c r="P35" s="16" t="inlineStr"/>
       <c r="Q35" s="16" t="inlineStr"/>
       <c r="R35" s="16" t="inlineStr">
         <is>
-          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S35" s="17" t="inlineStr">
@@ -4612,20 +4644,396 @@
         </is>
       </c>
       <c r="T35" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="U35" s="18" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="V35" s="18" t="n">
         <v>46281</v>
       </c>
       <c r="W35" s="16" t="inlineStr">
         <is>
+          <t>2026-09-16-activity-tracker-sync.md</t>
+        </is>
+      </c>
+      <c r="X35" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-intelligent-tracker-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Send out a skill-gap poll on HTML/CSS/JavaScript proficiency and use the results to build the training plan.</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Sarathchandra Babu</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>coordinate</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>Send the poll to the team and collect responses.</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr"/>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr"/>
+      <c r="N36" s="16" t="inlineStr"/>
+      <c r="O36" s="16" t="inlineStr">
+        <is>
+          <t>Or, if you can put a poll in one of these, let's see here.</t>
+        </is>
+      </c>
+      <c r="P36" s="16" t="inlineStr">
+        <is>
+          <t>D-2026-09-17-02</t>
+        </is>
+      </c>
+      <c r="Q36" s="16" t="inlineStr"/>
+      <c r="R36" s="16" t="inlineStr">
+        <is>
+          <t>Code Apps Learning Curriculum Structure Discussion</t>
+        </is>
+      </c>
+      <c r="S36" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T36" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="U36" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="V36" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="W36" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-17-code-apps-learning-curriculum-discussion.docx</t>
+        </is>
+      </c>
+      <c r="X36" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-17-unassigned-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Populate lsp_distributoremail for every distributor before the claim-status notification feature rolls out.</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Adwaith</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>Adwaith supplies the missing distributor email addresses for all distributor master records.</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr"/>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr"/>
+      <c r="N37" s="16" t="inlineStr"/>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>lsp_distributoremail is not populated for every distributor. Populate it before rollout or the notification silently sends to nobody.</t>
+        </is>
+      </c>
+      <c r="P37" s="16" t="inlineStr">
+        <is>
+          <t>CR section 7.4 Notifications</t>
+        </is>
+      </c>
+      <c r="Q37" s="16" t="inlineStr"/>
+      <c r="R37" s="16" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="S37" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T37" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U37" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V37" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W37" s="16" t="inlineStr">
+        <is>
           <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
         </is>
       </c>
-      <c r="X35" s="16" t="inlineStr">
+      <c r="X37" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16-lsp-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Brainstorm startup ideas during the walk (18 Sep, 17:00, ~30 min) and write them down afterwards</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>Write down the ideas after the walk</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr"/>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr"/>
+      <c r="N38" s="16" t="inlineStr"/>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>brainstorm startup ideas during the walk today, 18 Sep at 17:00, about 30 minutes. Personal, not tied to a project.</t>
+        </is>
+      </c>
+      <c r="P38" s="16" t="inlineStr">
+        <is>
+          <t>line itself: personal walk brainstorm task</t>
+        </is>
+      </c>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>basis unresolved</t>
+        </is>
+      </c>
+      <c r="R38" s="16" t="inlineStr">
+        <is>
+          <t>Personal note 2026-09-18</t>
+        </is>
+      </c>
+      <c r="S38" s="17" t="inlineStr">
+        <is>
+          <t>unplanned</t>
+        </is>
+      </c>
+      <c r="T38" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="U38" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="V38" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="W38" s="16" t="inlineStr">
+        <is>
+          <t>note-2026-09-18-walk-brainstorm.md</t>
+        </is>
+      </c>
+      <c r="X38" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-18-unassigned-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Agree and document a retention or archival policy for closed periodic closure line-item data.</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>lsp</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>unassigned</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>Ayush proposes a retention window and confirms it with the DMS side.</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr"/>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr"/>
+      <c r="N39" s="16" t="inlineStr"/>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>Agree a retention or archival policy for closed periodic closures.</t>
+        </is>
+      </c>
+      <c r="P39" s="16" t="inlineStr">
+        <is>
+          <t>CR section 8.6 Sizing</t>
+        </is>
+      </c>
+      <c r="Q39" s="16" t="inlineStr"/>
+      <c r="R39" s="16" t="inlineStr">
+        <is>
+          <t>CR: Distributor Line-Item Visibility and Claim Status Sync</t>
+        </is>
+      </c>
+      <c r="S39" s="17" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="T39" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="U39" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="V39" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="W39" s="16" t="inlineStr">
+        <is>
+          <t>CR_DISTRIBUTOR_LINE_ITEM_VISIBILITY_Revised (1).docx</t>
+        </is>
+      </c>
+      <c r="X39" s="16" t="inlineStr">
         <is>
           <t>2026-09-16-lsp-03</t>
         </is>

--- a/tracker/actions.xlsx
+++ b/tracker/actions.xlsx
@@ -1154,7 +1154,7 @@
     <row r="10">
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C10" s="11">
@@ -1181,7 +1181,7 @@
     <row r="11">
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C11" s="11">
@@ -1822,12 +1822,12 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Set and add the first demo date to the project plan.</t>
+          <t>Implement CR time-block functionality once the Time Logs data structure is finalized.</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
@@ -1837,12 +1837,10 @@
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>to_verify</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="n">
-        <v>46287</v>
-      </c>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="n"/>
       <c r="F2" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -1855,46 +1853,38 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>communicate</t>
-        </is>
-      </c>
-      <c r="I2" s="16" t="inlineStr">
-        <is>
-          <t>Confirm the demo date internally and message it to Sreekumar today.</t>
-        </is>
-      </c>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="inlineStr"/>
       <c r="J2" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>15m</t>
-        </is>
-      </c>
-      <c r="L2" s="16" t="inlineStr"/>
-      <c r="M2" s="16" t="inlineStr"/>
-      <c r="N2" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-22: due 2026-09-21 -&gt; 2026-09-22 | 2026-09-22: Sreekumar repeated the demo-date ask after it was already 2 days overdue; Ashwini committed to share it today. Escalating to P1 per repeat-ask rule. | 2026-09-25: Ashwini confirmed demo dates: Issues+CR demo next Wednesday (2026-09-30), Plan Tree demo on 2026-10-05; date already shared with Sreekumar. [I have shared you, sir, like maybe it's 9th, 5th, 9th of October, I guess, sorry, 5th of October, sir.]</t>
-        </is>
-      </c>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>Time Logs module completion</t>
+        </is>
+      </c>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>Time Logs data structure/module completion</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="inlineStr"/>
       <c r="O2" s="16" t="inlineStr">
         <is>
-          <t>No, please put the date where we can have the first demo.</t>
-        </is>
-      </c>
-      <c r="P2" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-21-intelligent-tracker-03</t>
-        </is>
-      </c>
-      <c r="Q2" s="16" t="inlineStr">
-        <is>
-          <t>due before meeting: 2026-09-22</t>
-        </is>
-      </c>
+          <t>functionality for that will not be done until the time logs is complete</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="inlineStr"/>
+      <c r="Q2" s="16" t="inlineStr"/>
       <c r="R2" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
@@ -1906,45 +1896,47 @@
         </is>
       </c>
       <c r="T2" s="18" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="U2" s="18" t="n"/>
       <c r="V2" s="18" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="W2" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-activity-tracker-sync.docx</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X2" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-03</t>
+          <t>2026-09-24-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Implement CR time-block functionality once the Time Logs data structure is finalized.</t>
+          <t>Verify and add date-based validation for inserting a new stage above or between existing stages in the plan tree.</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="n"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>46286</v>
+      </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -1957,37 +1949,33 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="I3" s="16" t="inlineStr"/>
-      <c r="J3" s="16" t="inlineStr">
-        <is>
-          <t>Laxmikant</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Add validation that checks a newly inserted stage's dates against neighboring stages' start/close dates.</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr"/>
       <c r="K3" s="17" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="L3" s="16" t="inlineStr">
-        <is>
-          <t>Time Logs module completion</t>
-        </is>
-      </c>
-      <c r="M3" s="16" t="inlineStr">
-        <is>
-          <t>Time Logs data structure/module completion</t>
-        </is>
-      </c>
+      <c r="L3" s="16" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr"/>
       <c r="N3" s="16" t="inlineStr"/>
       <c r="O3" s="16" t="inlineStr">
         <is>
-          <t>functionality for that will not be done until the time logs is complete</t>
-        </is>
-      </c>
-      <c r="P3" s="16" t="inlineStr"/>
+          <t>So, just okay, so we check that.</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>based on the dates, you have to get validation, cant be based on this date or the close date over here</t>
+        </is>
+      </c>
       <c r="Q3" s="16" t="inlineStr"/>
       <c r="R3" s="16" t="inlineStr">
         <is>
@@ -2000,27 +1988,27 @@
         </is>
       </c>
       <c r="T3" s="18" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="U3" s="18" t="n"/>
       <c r="V3" s="18" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="W3" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker- internal sync-up (5).docx</t>
+          <t>2026-09-21-activity-tracker-sync.docx</t>
         </is>
       </c>
       <c r="X3" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24-intelligent-tracker-05</t>
+          <t>2026-09-21-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Verify and add date-based validation for inserting a new stage above or between existing stages in the plan tree.</t>
+          <t>Add a 'my tasks' filter to the plan tree so team members can see only the tasks assigned to them.</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -2053,12 +2041,12 @@
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>build</t>
         </is>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>Add validation that checks a newly inserted stage's dates against neighboring stages' start/close dates.</t>
+          <t>Implement a my-tasks filter option on the plan tree screen.</t>
         </is>
       </c>
       <c r="J4" s="16" t="inlineStr"/>
@@ -2072,12 +2060,12 @@
       <c r="N4" s="16" t="inlineStr"/>
       <c r="O4" s="16" t="inlineStr">
         <is>
-          <t>So, just okay, so we check that.</t>
+          <t>Yes, yes, sir, we can give filters.</t>
         </is>
       </c>
       <c r="P4" s="16" t="inlineStr">
         <is>
-          <t>based on the dates, you have to get validation, cant be based on this date or the close date over here</t>
+          <t>So my task or something like that, if you can give, that makes easy, you know, life easy for them.</t>
         </is>
       </c>
       <c r="Q4" s="16" t="inlineStr"/>
@@ -2105,19 +2093,19 @@
       </c>
       <c r="X4" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-01</t>
+          <t>2026-09-21-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Add a 'my tasks' filter to the plan tree so team members can see only the tasks assigned to them.</t>
+          <t>Share the full project plan through UAT with Sreekumar, including the date it will be available.</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -2131,7 +2119,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -2145,18 +2133,18 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>communicate</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t>Implement a my-tasks filter option on the plan tree screen.</t>
+          <t>Confirm the full-plan-through-UAT availability date and send it to Sreekumar.</t>
         </is>
       </c>
       <c r="J5" s="16" t="inlineStr"/>
       <c r="K5" s="17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="L5" s="16" t="inlineStr"/>
@@ -2164,18 +2152,18 @@
       <c r="N5" s="16" t="inlineStr"/>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>Yes, yes, sir, we can give filters.</t>
+          <t>I just want to go through the full plan of this application till UAT.</t>
         </is>
       </c>
       <c r="P5" s="16" t="inlineStr">
         <is>
-          <t>So my task or something like that, if you can give, that makes easy, you know, life easy for them.</t>
+          <t>Sreekumar's request in this meeting</t>
         </is>
       </c>
       <c r="Q5" s="16" t="inlineStr"/>
       <c r="R5" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S5" s="17" t="inlineStr">
@@ -2184,32 +2172,32 @@
         </is>
       </c>
       <c r="T5" s="18" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="U5" s="18" t="n"/>
       <c r="V5" s="18" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="W5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-activity-tracker-sync.docx</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-21-intelligent-tracker-02</t>
+          <t>2026-09-22-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Share the full project plan through UAT with Sreekumar, including the date it will be available.</t>
+          <t>Build the checklist items and add-dependency screens in the plan tree.</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -2223,7 +2211,7 @@
         </is>
       </c>
       <c r="E6" s="18" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
@@ -2237,18 +2225,14 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>communicate</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>Confirm the full-plan-through-UAT availability date and send it to Sreekumar.</t>
-        </is>
-      </c>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr"/>
       <c r="J6" s="16" t="inlineStr"/>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L6" s="16" t="inlineStr"/>
@@ -2256,18 +2240,14 @@
       <c r="N6" s="16" t="inlineStr"/>
       <c r="O6" s="16" t="inlineStr">
         <is>
-          <t>I just want to go through the full plan of this application till UAT.</t>
-        </is>
-      </c>
-      <c r="P6" s="16" t="inlineStr">
-        <is>
-          <t>Sreekumar's request in this meeting</t>
-        </is>
-      </c>
+          <t>Lakshmi will be working on what is it, checklist items and add dependency, whatever his screens</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr"/>
       <c r="Q6" s="16" t="inlineStr"/>
       <c r="R6" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up (2026-09-22)</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S6" s="17" t="inlineStr">
@@ -2280,28 +2260,28 @@
       </c>
       <c r="U6" s="18" t="n"/>
       <c r="V6" s="18" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="W6" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker-Internal Sync-up.docx</t>
+          <t>Activity Tracker- internal sync-up (5).docx</t>
         </is>
       </c>
       <c r="X6" s="16" t="inlineStr">
         <is>
-          <t>2026-09-22-intelligent-tracker-02</t>
+          <t>2026-09-24-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Build the checklist items and add-dependency screens in the plan tree.</t>
+          <t>Continue building the create functionality for the Change Request module.</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -2344,7 +2324,7 @@
       <c r="N7" s="16" t="inlineStr"/>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi will be working on what is it, checklist items and add dependency, whatever his screens</t>
+          <t>these Johan and Sam will be working on create functionality</t>
         </is>
       </c>
       <c r="P7" s="16" t="inlineStr"/>
@@ -2373,19 +2353,19 @@
       </c>
       <c r="X7" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24-intelligent-tracker-01</t>
+          <t>2026-09-24-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Continue building the create functionality for the Change Request module.</t>
+          <t>Continue building the create functionality for the Issues module.</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -2457,19 +2437,19 @@
       </c>
       <c r="X8" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24-intelligent-tracker-02</t>
+          <t>2026-09-24-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Continue building the create functionality for the Issues module.</t>
+          <t>Send a group mail summarizing today's roadblocks.</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -2497,14 +2477,14 @@
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>communicate</t>
         </is>
       </c>
       <c r="I9" s="16" t="inlineStr"/>
       <c r="J9" s="16" t="inlineStr"/>
       <c r="K9" s="17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>15m</t>
         </is>
       </c>
       <c r="L9" s="16" t="inlineStr"/>
@@ -2512,7 +2492,7 @@
       <c r="N9" s="16" t="inlineStr"/>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>these Johan and Sam will be working on create functionality</t>
+          <t>The road breaks are happening, then just, I'll put that in group mail, actually.</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr"/>
@@ -2541,19 +2521,19 @@
       </c>
       <c r="X9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24-intelligent-tracker-03</t>
+          <t>2026-09-24-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Send a group mail summarizing today's roadblocks.</t>
+          <t>Review the CAPA workflow document comparing Azure DevOps, Viva Vault and SAP in detail.</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2567,28 +2547,28 @@
         </is>
       </c>
       <c r="E10" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>communicate</t>
+          <t>review</t>
         </is>
       </c>
       <c r="I10" s="16" t="inlineStr"/>
       <c r="J10" s="16" t="inlineStr"/>
       <c r="K10" s="17" t="inlineStr">
         <is>
-          <t>15m</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L10" s="16" t="inlineStr"/>
@@ -2596,14 +2576,18 @@
       <c r="N10" s="16" t="inlineStr"/>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>The road breaks are happening, then just, I'll put that in group mail, actually.</t>
+          <t>even I have to go through this workflow in detail</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr"/>
-      <c r="Q10" s="16" t="inlineStr"/>
+      <c r="Q10" s="16" t="inlineStr">
+        <is>
+          <t>owner unknown: Aswin</t>
+        </is>
+      </c>
       <c r="R10" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up</t>
+          <t>CAPA - Discussion On Existing System's</t>
         </is>
       </c>
       <c r="S10" s="17" t="inlineStr">
@@ -2612,32 +2596,32 @@
         </is>
       </c>
       <c r="T10" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="U10" s="18" t="n"/>
       <c r="V10" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="W10" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker- internal sync-up (5).docx</t>
+          <t>CAPA - Discussion On Existing System's .docx</t>
         </is>
       </c>
       <c r="X10" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24-intelligent-tracker-04</t>
+          <t>2026-09-25-unassigned-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Review the CAPA workflow document comparing Azure DevOps, Viva Vault and SAP in detail.</t>
+          <t>Check off items on the shared list comparing existing CAPA systems.</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Aswin</t>
+          <t>Thenappan</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2680,13 +2664,13 @@
       <c r="N11" s="16" t="inlineStr"/>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>even I have to go through this workflow in detail</t>
+          <t>So I'll just cheque it off</t>
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr"/>
       <c r="Q11" s="16" t="inlineStr">
         <is>
-          <t>owner unknown: Aswin</t>
+          <t>owner unknown: Thenappan</t>
         </is>
       </c>
       <c r="R11" s="16" t="inlineStr">
@@ -2713,19 +2697,19 @@
       </c>
       <c r="X11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-25-unassigned-01</t>
+          <t>2026-09-25-unassigned-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Check off items on the shared list comparing existing CAPA systems.</t>
+          <t>Add newly identified system-comparison items to the shared Excel file with Thenappan.</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Thenappan</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -2753,7 +2737,7 @@
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>coordinate</t>
         </is>
       </c>
       <c r="I12" s="16" t="inlineStr"/>
@@ -2768,13 +2752,13 @@
       <c r="N12" s="16" t="inlineStr"/>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>So I'll just cheque it off</t>
+          <t>we can get a few more things, then we will add it in the same Excel</t>
         </is>
       </c>
       <c r="P12" s="16" t="inlineStr"/>
       <c r="Q12" s="16" t="inlineStr">
         <is>
-          <t>owner unknown: Thenappan</t>
+          <t>owner unknown: Aswin</t>
         </is>
       </c>
       <c r="R12" s="16" t="inlineStr">
@@ -2801,19 +2785,19 @@
       </c>
       <c r="X12" s="16" t="inlineStr">
         <is>
-          <t>2026-09-25-unassigned-02</t>
+          <t>2026-09-25-unassigned-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Add newly identified system-comparison items to the shared Excel file with Thenappan.</t>
+          <t>Publish a weekly plan every Monday showing the team's planned activities and dates.</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Aswin</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -2827,28 +2811,32 @@
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>Intelligent Tracker</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>coordinate</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr"/>
+          <t>communicate</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Draft and share the first weekly plan covering the week starting September 28.</t>
+        </is>
+      </c>
       <c r="J13" s="16" t="inlineStr"/>
       <c r="K13" s="17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="L13" s="16" t="inlineStr"/>
@@ -2856,18 +2844,18 @@
       <c r="N13" s="16" t="inlineStr"/>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>we can get a few more things, then we will add it in the same Excel</t>
-        </is>
-      </c>
-      <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr">
-        <is>
-          <t>owner unknown: Aswin</t>
-        </is>
-      </c>
+          <t>I want you to publish a weekly plan going forward from every Monday.</t>
+        </is>
+      </c>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>Sreekumar's directive in this meeting</t>
+        </is>
+      </c>
+      <c r="Q13" s="16" t="inlineStr"/>
       <c r="R13" s="16" t="inlineStr">
         <is>
-          <t>CAPA - Discussion On Existing System's</t>
+          <t>Activity Tracker internal sync-up (2026-09-22)</t>
         </is>
       </c>
       <c r="S13" s="17" t="inlineStr">
@@ -2876,32 +2864,32 @@
         </is>
       </c>
       <c r="T13" s="18" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="U13" s="18" t="n"/>
       <c r="V13" s="18" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="W13" s="16" t="inlineStr">
         <is>
-          <t>CAPA - Discussion On Existing System's .docx</t>
+          <t>Activity Tracker-Internal Sync-up.docx</t>
         </is>
       </c>
       <c r="X13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-25-unassigned-03</t>
+          <t>2026-09-22-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Publish a weekly plan every Monday showing the team's planned activities and dates.</t>
+          <t>Add a rework checkbox to tasks created under an issue, defaulting to checked, editable per task by the TL or PM.</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -2914,9 +2902,7 @@
           <t>open</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
-        <v>46293</v>
-      </c>
+      <c r="E14" s="18" t="n"/>
       <c r="F14" s="16" t="inlineStr">
         <is>
           <t>intelligent-tracker</t>
@@ -2929,18 +2915,18 @@
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>communicate</t>
+          <t>build</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>Draft and share the first weekly plan covering the week starting September 28.</t>
+          <t>Add the rework checkbox to the task creation form in the Issues module, default checked, with TL/PM override per task.</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr"/>
       <c r="K14" s="17" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>half-day</t>
         </is>
       </c>
       <c r="L14" s="16" t="inlineStr"/>
@@ -2948,12 +2934,12 @@
       <c r="N14" s="16" t="inlineStr"/>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>I want you to publish a weekly plan going forward from every Monday.</t>
+          <t>By default, let it be a rework, but the TL or the project manager can make it not a rework.</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr">
         <is>
-          <t>Sreekumar's directive in this meeting</t>
+          <t>Sreekumar's rework checkbox decision in this meeting</t>
         </is>
       </c>
       <c r="Q14" s="16" t="inlineStr"/>
@@ -2981,24 +2967,24 @@
       </c>
       <c r="X14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-22-intelligent-tracker-01</t>
+          <t>2026-09-22-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Add a rework checkbox to tasks created under an issue, defaulting to checked, editable per task by the TL or PM.</t>
+          <t>Decide with Thenappan which existing system approach is best and report the choice to the team.</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Aswin</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -3009,28 +2995,24 @@
       <c r="E15" s="18" t="n"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>intelligent-tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>Intelligent Tracker</t>
+          <t>unassigned</t>
         </is>
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>Add the rework checkbox to the task creation form in the Issues module, default checked, with TL/PM override per task.</t>
-        </is>
-      </c>
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr"/>
       <c r="J15" s="16" t="inlineStr"/>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>half-day</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L15" s="16" t="inlineStr"/>
@@ -3038,18 +3020,18 @@
       <c r="N15" s="16" t="inlineStr"/>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>By default, let it be a rework, but the TL or the project manager can make it not a rework.</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
-        <is>
-          <t>Sreekumar's rework checkbox decision in this meeting</t>
-        </is>
-      </c>
-      <c r="Q15" s="16" t="inlineStr"/>
+          <t>In time, I will update, which I feel is better, OK</t>
+        </is>
+      </c>
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr">
+        <is>
+          <t>owner unknown: Aswin</t>
+        </is>
+      </c>
       <c r="R15" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker internal sync-up (2026-09-22)</t>
+          <t>CAPA - Discussion On Existing System's</t>
         </is>
       </c>
       <c r="S15" s="17" t="inlineStr">
@@ -3058,84 +3040,74 @@
         </is>
       </c>
       <c r="T15" s="18" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="U15" s="18" t="n"/>
       <c r="V15" s="18" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="W15" s="16" t="inlineStr">
         <is>
-          <t>Activity Tracker-Internal Sync-up.docx</t>
+          <t>CAPA - Discussion On Existing System's .docx</t>
         </is>
       </c>
       <c r="X15" s="16" t="inlineStr">
         <is>
-          <t>2026-09-22-intelligent-tracker-03</t>
+          <t>2026-09-25-unassigned-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Decide with Thenappan which existing system approach is best and report the choice to the team.</t>
+          <t>Sign off on the reviewed database design after today's walkthrough.</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Aswin</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>46276</v>
+      </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>intelligent-tracker</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>decide</t>
-        </is>
-      </c>
+          <t>Intelligent Tracker</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr"/>
       <c r="I16" s="16" t="inlineStr"/>
       <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="K16" s="17" t="inlineStr"/>
       <c r="L16" s="16" t="inlineStr"/>
       <c r="M16" s="16" t="inlineStr"/>
       <c r="N16" s="16" t="inlineStr"/>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>In time, I will update, which I feel is better, OK</t>
+          <t>I will be signing off on the Debi after the review</t>
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr"/>
-      <c r="Q16" s="16" t="inlineStr">
-        <is>
-          <t>owner unknown: Aswin</t>
-        </is>
-      </c>
+      <c r="Q16" s="16" t="inlineStr"/>
       <c r="R16" s="16" t="inlineStr">
         <is>
-          <t>CAPA - Discussion On Existing System's</t>
+          <t>Activity Tracker internal sync-up</t>
         </is>
       </c>
       <c r="S16" s="17" t="inlineStr">
@@ -3144,32 +3116,34 @@
         </is>
       </c>
       <c r="T16" s="18" t="n">
-        <v>46290</v>
-      </c>
-      <c r="U16" s="18" t="n"/>
+        <v>46282</v>
+      </c>
+      <c r="U16" s="18" t="n">
+        <v>46282</v>
+      </c>
       <c r="V16" s="18" t="n">
-        <v>46290</v>
+        <v>46276</v>
       </c>
       <c r="W16" s="16" t="inlineStr">
         <is>
-          <t>CAPA - Discussion On Existing System's .docx</t>
+          <t>2026-09-11-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X16" s="16" t="inlineStr">
         <is>
-          <t>2026-09-25-unassigned-04</t>
+          <t>2026-09-11-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Sign off on the reviewed database design after today's walkthrough.</t>
+          <t>Work with Ashwini on the overall workflow solution design document.</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Ashwini</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -3204,7 +3178,7 @@
       <c r="N17" s="16" t="inlineStr"/>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>I will be signing off on the Debi after the review</t>
+          <t>Lakshmi and I will be working on the proper workflow solution design</t>
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr"/>
@@ -3235,19 +3209,19 @@
       </c>
       <c r="X17" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-01</t>
+          <t>2026-09-11-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Work with Ashwini on the overall workflow solution design document.</t>
+          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -3282,7 +3256,7 @@
       <c r="N18" s="16" t="inlineStr"/>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi and I will be working on the proper workflow solution design</t>
+          <t>Change the UI. I'll change it.</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr"/>
@@ -3313,14 +3287,14 @@
       </c>
       <c r="X18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-04</t>
+          <t>2026-09-11-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Change the CR Notes field UI from a single-line text box to a multi-line text box as Sreekumar requested.</t>
+          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
@@ -3360,7 +3334,7 @@
       <c r="N19" s="16" t="inlineStr"/>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>Change the UI. I'll change it.</t>
+          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr"/>
@@ -3391,19 +3365,19 @@
       </c>
       <c r="X19" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-05</t>
+          <t>2026-09-11-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Change Request module workflow and share them with Ashwini and Laxmikant.</t>
+          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -3438,7 +3412,7 @@
       <c r="N20" s="16" t="inlineStr"/>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>you share it to Ashwini B and Lakshmi Lakshmi</t>
+          <t>user stories you figure out and you show me</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr"/>
@@ -3469,19 +3443,19 @@
       </c>
       <c r="X20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-06</t>
+          <t>2026-09-11-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Write detailed user stories for the Issues module workflow and present them to Ayush.</t>
+          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -3495,7 +3469,7 @@
         </is>
       </c>
       <c r="E21" s="18" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
@@ -3516,7 +3490,7 @@
       <c r="N21" s="16" t="inlineStr"/>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>user stories you figure out and you show me</t>
+          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr"/>
@@ -3538,28 +3512,28 @@
         <v>46282</v>
       </c>
       <c r="V21" s="18" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="W21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-activity-tracker-sync.md</t>
+          <t>2026-09-15-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-11-intelligent-tracker-07</t>
+          <t>2026-09-15-intelligent-tracker-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Complete the SharePoint list configuration for the DB changes made last Friday and update the UI design to match.</t>
+          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -3573,7 +3547,7 @@
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
@@ -3591,10 +3565,14 @@
       <c r="K22" s="17" t="inlineStr"/>
       <c r="L22" s="16" t="inlineStr"/>
       <c r="M22" s="16" t="inlineStr"/>
-      <c r="N22" s="16" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
+        </is>
+      </c>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>Lakshmi will be doing the SharePoint configuration, whatever related to DB changes last Friday we did.</t>
+          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
         </is>
       </c>
       <c r="P22" s="16" t="inlineStr"/>
@@ -3610,10 +3588,10 @@
         </is>
       </c>
       <c r="T22" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="V22" s="18" t="n">
         <v>46280</v>
@@ -3625,19 +3603,19 @@
       </c>
       <c r="X22" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-01</t>
+          <t>2026-09-15-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Update the Issues module UI design and start Canvas development once it is complete.</t>
+          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -3669,14 +3647,10 @@
       <c r="K23" s="17" t="inlineStr"/>
       <c r="L23" s="16" t="inlineStr"/>
       <c r="M23" s="16" t="inlineStr"/>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-16: Sreekumar added new review points (root cause, resolution, attachment capture, status dropdown) that must be incorporated before this task is complete; due date extended to today.</t>
-        </is>
-      </c>
+      <c r="N23" s="16" t="inlineStr"/>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>Samuel also, he will update the UI design. So if it is done, so he will start with the development.</t>
+          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr"/>
@@ -3698,28 +3672,28 @@
         <v>46283</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="W23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-activity-tracker-sync.md</t>
+          <t>2026-09-16-activity-tracker-sync.md</t>
         </is>
       </c>
       <c r="X23" s="16" t="inlineStr">
         <is>
-          <t>2026-09-15-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Add the currency selector column to the CR entry screen UI (currently only present in the impact analysis view).</t>
+          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Laxmikant</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -3754,7 +3728,7 @@
       <c r="N24" s="16" t="inlineStr"/>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>you'll be adding that column in that entry screen, CR entry screen. It is not there now.</t>
+          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
         </is>
       </c>
       <c r="P24" s="16" t="inlineStr"/>
@@ -3785,14 +3759,14 @@
       </c>
       <c r="X24" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-03</t>
+          <t>2026-09-16-intelligent-tracker-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Add phase-level delay visibility (green/red per stage, payment milestone impact) and a morning alert for predicted delays to the project screen.</t>
+          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
@@ -3832,7 +3806,7 @@
       <c r="N25" s="16" t="inlineStr"/>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>Every day morning they should know that what is a predicted problem that can happen in the future.</t>
+          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr"/>
@@ -3863,19 +3837,19 @@
       </c>
       <c r="X25" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-04</t>
+          <t>2026-09-16-intelligent-tracker-05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Add separate flags for CR effort-vs-estimate overrun and schedule slip in the time tracker.</t>
+          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Laxmikant</t>
+          <t>Ayush</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -3910,7 +3884,7 @@
       <c r="N26" s="16" t="inlineStr"/>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>there will be definitely a flat. Yes, estimated hours versus total hours will be there, sir.</t>
+          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr"/>
@@ -3941,19 +3915,19 @@
       </c>
       <c r="X26" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-05</t>
+          <t>2026-09-16-intelligent-tracker-07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Review Laxmikant's updated solution design document and sign off if it is acceptable.</t>
+          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Ayush</t>
+          <t>Ashwini</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
@@ -3988,7 +3962,7 @@
       <c r="N27" s="16" t="inlineStr"/>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>He sent it to me. I'll review it and I'll sign off on that if it is okay.</t>
+          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr"/>
@@ -4004,10 +3978,10 @@
         </is>
       </c>
       <c r="T27" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="U27" s="18" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="V27" s="18" t="n">
         <v>46281</v>
@@ -4019,14 +3993,14 @@
       </c>
       <c r="X27" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-07</t>
+          <t>2026-09-16-intelligent-tracker-02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Review how developers close issues in Zoho (root cause, resolution, attachments) and identify fields to replicate in the Issues module UI.</t>
+          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
@@ -4066,7 +4040,7 @@
       <c r="N28" s="16" t="inlineStr"/>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>Ashwini, how a developer is closing a task? Just look at that once again in Zoho.</t>
+          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
         </is>
       </c>
       <c r="P28" s="16" t="inlineStr"/>
@@ -4097,14 +4071,14 @@
       </c>
       <c r="X28" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-02</t>
+          <t>2026-09-16-intelligent-tracker-06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Post today's review comments for Issues, CR and Plan Tree in the group chat so Sreekumar can give sign-off.</t>
+          <t>Set and add the first demo date to the project plan.</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
@@ -4123,7 +4097,7 @@
         </is>
       </c>
       <c r="E29" s="18" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -4135,20 +4109,48 @@
           <t>Intelligent Tracker</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
-      <c r="I29" s="16" t="inlineStr"/>
-      <c r="J29" s="16" t="inlineStr"/>
-      <c r="K29" s="17" t="inlineStr"/>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>communicate</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>Confirm the demo date internally and message it to Sreekumar today.</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>Ashwini</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>15m</t>
+        </is>
+      </c>
       <c r="L29" s="16" t="inlineStr"/>
       <c r="M29" s="16" t="inlineStr"/>
-      <c r="N29" s="16" t="inlineStr"/>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-22: due 2026-09-21 -&gt; 2026-09-22 | 2026-09-22: Sreekumar repeated the demo-date ask after it was already 2 days overdue; Ashwini committed to share it today. Escalating to P1 per repeat-ask rule. | 2026-09-25: Ashwini confirmed demo dates: Issues+CR demo next Wednesday (2026-09-30), Plan Tree demo on 2026-10-05; date already shared with Sreekumar. [I have shared you, sir, like maybe it's 9th, 5th, 9th of October, I guess, sorry, 5th of October, sir.]</t>
+        </is>
+      </c>
       <c r="O29" s="16" t="inlineStr">
         <is>
-          <t>make sure that we put those review comments in the group. Based on that, I will give you the sign off in the chat.</t>
-        </is>
-      </c>
-      <c r="P29" s="16" t="inlineStr"/>
-      <c r="Q29" s="16" t="inlineStr"/>
+          <t>No, please put the date where we can have the first demo.</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-21-intelligent-tracker-03</t>
+        </is>
+      </c>
+      <c r="Q29" s="16" t="inlineStr">
+        <is>
+          <t>due before meeting: 2026-09-22</t>
+        </is>
+      </c>
       <c r="R29" s="16" t="inlineStr">
         <is>
           <t>Activity Tracker internal sync-up</t>
@@ -4160,22 +4162,22 @@
         </is>
       </c>
       <c r="T29" s="18" t="n">
-        <v>46282</v>
+        <v>46290</v>
       </c>
       <c r="U29" s="18" t="n">
-        <v>46282</v>
+        <v>46290</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="W29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-activity-tracker-sync.md</t>
+          <t>2026-09-21-activity-tracker-sync.docx</t>
         </is>
       </c>
       <c r="X29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-16-intelligent-tracker-06</t>
+          <t>2026-09-21-intelligent-tracker-03</t>
         </is>
       </c>
     </row>
